--- a/research/traditional_assets/database/data/belgium/belgium_information_services.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_information_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtbr_keyw" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,37 +590,37 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0178</v>
+        <v>0.0299</v>
       </c>
       <c r="E2">
-        <v>-0.457</v>
+        <v>-0.141</v>
       </c>
       <c r="G2">
-        <v>0.06553763440860214</v>
+        <v>0.07455357142857143</v>
       </c>
       <c r="H2">
-        <v>0.03086021505376343</v>
+        <v>0.07455357142857143</v>
       </c>
       <c r="I2">
-        <v>-0.008333333333333333</v>
+        <v>0.05491071428571429</v>
       </c>
       <c r="J2">
-        <v>-0.005770887166236003</v>
+        <v>0.05491071428571429</v>
       </c>
       <c r="K2">
-        <v>0.268</v>
+        <v>1.12</v>
       </c>
       <c r="L2">
-        <v>0.01440860215053763</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="M2">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.001397849462365591</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.1455223880597015</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -630,79 +632,76 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.039</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1.75</v>
+        <v>2.72</v>
       </c>
       <c r="V2">
-        <v>0.06272401433691757</v>
+        <v>0.1088</v>
       </c>
       <c r="W2">
-        <v>0.008673139158576053</v>
+        <v>0.03446153846153847</v>
       </c>
       <c r="X2">
-        <v>0.0755630158999183</v>
+        <v>0.1390859047795637</v>
       </c>
       <c r="Y2">
-        <v>-0.06688987674134225</v>
+        <v>-0.1046243663180253</v>
       </c>
       <c r="Z2">
-        <v>0.754257907542579</v>
+        <v>0.9214315096668036</v>
       </c>
       <c r="AA2">
-        <v>-0.004352737278669491</v>
+        <v>0.05059646236116824</v>
       </c>
       <c r="AB2">
-        <v>0.07082949342258638</v>
+        <v>0.1302967105278441</v>
       </c>
       <c r="AC2">
-        <v>-0.07518223070125586</v>
+        <v>-0.07970024816667581</v>
       </c>
       <c r="AD2">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="AG2">
-        <v>0.9199999999999999</v>
+        <v>-0.2600000000000002</v>
       </c>
       <c r="AH2">
-        <v>0.0873405299313052</v>
+        <v>0.0895848506919155</v>
       </c>
       <c r="AI2">
-        <v>0.07527488018043417</v>
+        <v>0.07555282555282555</v>
       </c>
       <c r="AJ2">
-        <v>0.03192227619708535</v>
+        <v>-0.01050929668552952</v>
       </c>
       <c r="AK2">
-        <v>0.02728351126927639</v>
+        <v>-0.008713136729222528</v>
       </c>
       <c r="AL2">
-        <v>0.068</v>
+        <v>0.114</v>
       </c>
       <c r="AM2">
-        <v>-0.724</v>
+        <v>-0.406</v>
       </c>
       <c r="AN2">
-        <v>3.814285714285715</v>
+        <v>0.8785714285714287</v>
       </c>
       <c r="AO2">
-        <v>-2.279411764705882</v>
+        <v>10.78947368421053</v>
       </c>
       <c r="AP2">
-        <v>1.314285714285714</v>
+        <v>-0.09285714285714294</v>
       </c>
       <c r="AQ2">
-        <v>0.2140883977900553</v>
+        <v>-3.029556650246305</v>
       </c>
     </row>
     <row r="3">
@@ -722,37 +721,37 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0178</v>
+        <v>0.0299</v>
       </c>
       <c r="E3">
-        <v>-0.457</v>
+        <v>-0.141</v>
       </c>
       <c r="G3">
-        <v>0.06553763440860214</v>
+        <v>0.07455357142857143</v>
       </c>
       <c r="H3">
-        <v>0.03086021505376343</v>
+        <v>0.07455357142857143</v>
       </c>
       <c r="I3">
-        <v>-0.008333333333333333</v>
+        <v>0.05491071428571429</v>
       </c>
       <c r="J3">
-        <v>-0.005770887166236003</v>
+        <v>0.05491071428571429</v>
       </c>
       <c r="K3">
-        <v>0.268</v>
+        <v>1.12</v>
       </c>
       <c r="L3">
-        <v>0.01440860215053763</v>
+        <v>0.05000000000000001</v>
       </c>
       <c r="M3">
-        <v>0.039</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.001397849462365591</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.1455223880597015</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -764,79 +763,8788 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0.039</v>
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>2.72</v>
+      </c>
+      <c r="V3">
+        <v>0.1088</v>
+      </c>
+      <c r="W3">
+        <v>0.03446153846153847</v>
+      </c>
+      <c r="X3">
+        <v>0.1390859047795637</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1046243663180253</v>
+      </c>
+      <c r="Z3">
+        <v>0.9214315096668036</v>
+      </c>
+      <c r="AA3">
+        <v>0.05059646236116824</v>
+      </c>
+      <c r="AB3">
+        <v>0.1302967105278441</v>
+      </c>
+      <c r="AC3">
+        <v>-0.07970024816667581</v>
+      </c>
+      <c r="AD3">
+        <v>2.46</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>2.46</v>
+      </c>
+      <c r="AG3">
+        <v>-0.2600000000000002</v>
+      </c>
+      <c r="AH3">
+        <v>0.0895848506919155</v>
+      </c>
+      <c r="AI3">
+        <v>0.07555282555282555</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.01050929668552952</v>
+      </c>
+      <c r="AK3">
+        <v>-0.008713136729222528</v>
+      </c>
+      <c r="AL3">
+        <v>0.114</v>
+      </c>
+      <c r="AM3">
+        <v>-0.406</v>
+      </c>
+      <c r="AN3">
+        <v>0.8785714285714287</v>
+      </c>
+      <c r="AO3">
+        <v>10.78947368421053</v>
+      </c>
+      <c r="AP3">
+        <v>-0.09285714285714294</v>
+      </c>
+      <c r="AQ3">
+        <v>-3.029556650246305</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Keyware Technologies NV (ENXTBR:KEYW)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTBR:KEYW</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Information Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0895848506919155</v>
+      </c>
+      <c r="F2">
+        <v>0.18</v>
+      </c>
+      <c r="G2">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>23.0319600927718</v>
+      </c>
+      <c r="I2">
+        <v>24.74</v>
+      </c>
+      <c r="J2">
+        <v>25.2547600927718</v>
+      </c>
+      <c r="K2">
+        <v>2.46</v>
+      </c>
+      <c r="L2">
+        <v>4.9428</v>
+      </c>
+      <c r="M2">
+        <v>0.130296710527844</v>
+      </c>
+      <c r="N2">
+        <v>0.128431760909372</v>
+      </c>
+      <c r="O2">
+        <v>0.040975630733945</v>
+      </c>
+      <c r="P2">
+        <v>0.04125</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.139085904779564</v>
+      </c>
+      <c r="T2">
+        <v>0.147569220621185</v>
+      </c>
+      <c r="U2">
+        <v>1.4432083195755</v>
+      </c>
+      <c r="V2">
+        <v>1.56529119879094</v>
+      </c>
+      <c r="W2">
+        <v>4.524487408682601</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>25</v>
+      </c>
+      <c r="AB2">
+        <v>0.06948816980840411</v>
+      </c>
+      <c r="AC2">
+        <v>0.0546341743119266</v>
+      </c>
+      <c r="AD2">
+        <v>0.25</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>2.8</v>
+      </c>
+      <c r="AH2">
+        <v>1.57</v>
+      </c>
+      <c r="AI2">
+        <v>1.891</v>
+      </c>
+      <c r="AJ2">
+        <v>2.46</v>
+      </c>
+      <c r="AK2">
+        <v>2.46</v>
+      </c>
+      <c r="AL2">
+        <v>0.114</v>
+      </c>
+      <c r="AM2">
+        <v>2.46</v>
+      </c>
+      <c r="AN2">
+        <v>2.72</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1321934669208081</v>
+      </c>
+      <c r="C2">
+        <v>26.95754779740943</v>
+      </c>
+      <c r="D2">
+        <v>24.23754779740943</v>
+      </c>
+      <c r="E2">
+        <v>-2.46</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2.72</v>
+      </c>
+      <c r="H2">
+        <v>25</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2.8</v>
+      </c>
+      <c r="K2">
+        <v>1.57</v>
+      </c>
+      <c r="L2">
+        <v>1.23</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.23</v>
+      </c>
+      <c r="O2">
+        <v>0.3074999999999999</v>
+      </c>
+      <c r="P2">
+        <v>0.9224999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>2.4925</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1321934669208081</v>
+      </c>
+      <c r="T2">
+        <v>1.344019668071799</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.034275</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1319147332535061</v>
+      </c>
+      <c r="C3">
+        <v>26.75550152062728</v>
+      </c>
+      <c r="D3">
+        <v>24.31010152062728</v>
+      </c>
+      <c r="E3">
+        <v>-2.1854</v>
+      </c>
+      <c r="F3">
+        <v>0.2746</v>
+      </c>
+      <c r="G3">
+        <v>2.72</v>
+      </c>
+      <c r="H3">
+        <v>25</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2.8</v>
+      </c>
+      <c r="K3">
+        <v>1.57</v>
+      </c>
+      <c r="L3">
+        <v>1.23</v>
+      </c>
+      <c r="M3">
+        <v>0.01254922</v>
+      </c>
+      <c r="N3">
+        <v>1.21745078</v>
+      </c>
+      <c r="O3">
+        <v>0.304362695</v>
+      </c>
+      <c r="P3">
+        <v>0.9130880849999998</v>
+      </c>
+      <c r="Q3">
+        <v>2.483088085</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1329009931853597</v>
       </c>
       <c r="T3">
+        <v>1.354201635254161</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.034275</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>98.01405983798193</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1316359995862041</v>
+      </c>
+      <c r="C4">
+        <v>26.553890918916</v>
+      </c>
+      <c r="D4">
+        <v>24.383090918916</v>
+      </c>
+      <c r="E4">
+        <v>-1.9108</v>
+      </c>
+      <c r="F4">
+        <v>0.5492</v>
+      </c>
+      <c r="G4">
+        <v>2.72</v>
+      </c>
+      <c r="H4">
+        <v>25</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2.8</v>
+      </c>
+      <c r="K4">
+        <v>1.57</v>
+      </c>
+      <c r="L4">
+        <v>1.23</v>
+      </c>
+      <c r="M4">
+        <v>0.02509844</v>
+      </c>
+      <c r="N4">
+        <v>1.20490156</v>
+      </c>
+      <c r="O4">
+        <v>0.3012253899999999</v>
+      </c>
+      <c r="P4">
+        <v>0.9036761699999998</v>
+      </c>
+      <c r="Q4">
+        <v>2.47367617</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1336229587614327</v>
+      </c>
+      <c r="T4">
+        <v>1.364591397685143</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.034275</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>49.00702991899097</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.131357265918902</v>
+      </c>
+      <c r="C5">
+        <v>26.35271992834616</v>
+      </c>
+      <c r="D5">
+        <v>24.45651992834616</v>
+      </c>
+      <c r="E5">
+        <v>-1.6362</v>
+      </c>
+      <c r="F5">
+        <v>0.8238</v>
+      </c>
+      <c r="G5">
+        <v>2.72</v>
+      </c>
+      <c r="H5">
+        <v>25</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2.8</v>
+      </c>
+      <c r="K5">
+        <v>1.57</v>
+      </c>
+      <c r="L5">
+        <v>1.23</v>
+      </c>
+      <c r="M5">
+        <v>0.03764766</v>
+      </c>
+      <c r="N5">
+        <v>1.19235234</v>
+      </c>
+      <c r="O5">
+        <v>0.2980880849999999</v>
+      </c>
+      <c r="P5">
+        <v>0.8942642549999998</v>
+      </c>
+      <c r="Q5">
+        <v>2.464264255</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1343598102256722</v>
+      </c>
+      <c r="T5">
+        <v>1.375195382021918</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.034275</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>32.67135327932732</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1310785322516</v>
+      </c>
+      <c r="C6">
+        <v>26.151992532545</v>
+      </c>
+      <c r="D6">
+        <v>24.530392532545</v>
+      </c>
+      <c r="E6">
+        <v>-1.3616</v>
+      </c>
+      <c r="F6">
+        <v>1.0984</v>
+      </c>
+      <c r="G6">
+        <v>2.72</v>
+      </c>
+      <c r="H6">
+        <v>25</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2.8</v>
+      </c>
+      <c r="K6">
+        <v>1.57</v>
+      </c>
+      <c r="L6">
+        <v>1.23</v>
+      </c>
+      <c r="M6">
+        <v>0.05019688000000001</v>
+      </c>
+      <c r="N6">
+        <v>1.17980312</v>
+      </c>
+      <c r="O6">
+        <v>0.2949507799999999</v>
+      </c>
+      <c r="P6">
+        <v>0.8848523399999997</v>
+      </c>
+      <c r="Q6">
+        <v>2.45485234</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1351120127620833</v>
+      </c>
+      <c r="T6">
+        <v>1.386020282699043</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.034275</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>24.50351495949548</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.130799798584298</v>
+      </c>
+      <c r="C7">
+        <v>25.95171276341692</v>
+      </c>
+      <c r="D7">
+        <v>24.60471276341692</v>
+      </c>
+      <c r="E7">
+        <v>-1.087</v>
+      </c>
+      <c r="F7">
+        <v>1.373</v>
+      </c>
+      <c r="G7">
+        <v>2.72</v>
+      </c>
+      <c r="H7">
+        <v>25</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2.8</v>
+      </c>
+      <c r="K7">
+        <v>1.57</v>
+      </c>
+      <c r="L7">
+        <v>1.23</v>
+      </c>
+      <c r="M7">
+        <v>0.06274610000000001</v>
+      </c>
+      <c r="N7">
+        <v>1.1672539</v>
+      </c>
+      <c r="O7">
+        <v>0.2918134749999999</v>
+      </c>
+      <c r="P7">
+        <v>0.8754404249999999</v>
+      </c>
+      <c r="Q7">
+        <v>2.445440425</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1358800511413663</v>
+      </c>
+      <c r="T7">
+        <v>1.397073076022001</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.034275</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>19.60281196759638</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1305210649169959</v>
+      </c>
+      <c r="C8">
+        <v>25.75188470187693</v>
+      </c>
+      <c r="D8">
+        <v>24.67948470187693</v>
+      </c>
+      <c r="E8">
+        <v>-0.8124</v>
+      </c>
+      <c r="F8">
+        <v>1.6476</v>
+      </c>
+      <c r="G8">
+        <v>2.72</v>
+      </c>
+      <c r="H8">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2.8</v>
+      </c>
+      <c r="K8">
+        <v>1.57</v>
+      </c>
+      <c r="L8">
+        <v>1.23</v>
+      </c>
+      <c r="M8">
+        <v>0.07529532</v>
+      </c>
+      <c r="N8">
+        <v>1.15470468</v>
+      </c>
+      <c r="O8">
+        <v>0.28867617</v>
+      </c>
+      <c r="P8">
+        <v>0.8660285099999998</v>
+      </c>
+      <c r="Q8">
+        <v>2.43602851</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1366644307627617</v>
+      </c>
+      <c r="T8">
+        <v>1.408361035160342</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.034275</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>16.33567663966366</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1302423312496939</v>
+      </c>
+      <c r="C9">
+        <v>25.55251247859769</v>
+      </c>
+      <c r="D9">
+        <v>24.7547124785977</v>
+      </c>
+      <c r="E9">
+        <v>-0.5377999999999996</v>
+      </c>
+      <c r="F9">
+        <v>1.9222</v>
+      </c>
+      <c r="G9">
+        <v>2.72</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2.8</v>
+      </c>
+      <c r="K9">
+        <v>1.57</v>
+      </c>
+      <c r="L9">
+        <v>1.23</v>
+      </c>
+      <c r="M9">
+        <v>0.08784454000000003</v>
+      </c>
+      <c r="N9">
+        <v>1.14215546</v>
+      </c>
+      <c r="O9">
+        <v>0.2855388649999999</v>
+      </c>
+      <c r="P9">
+        <v>0.8566165949999998</v>
+      </c>
+      <c r="Q9">
+        <v>2.426616595</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1374656787631118</v>
+      </c>
+      <c r="T9">
+        <v>1.41989174610811</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.034275</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>14.00200854828313</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.130059597582392</v>
+      </c>
+      <c r="C10">
+        <v>25.32748008040676</v>
+      </c>
+      <c r="D10">
+        <v>24.80428008040676</v>
+      </c>
+      <c r="E10">
+        <v>-0.2631999999999999</v>
+      </c>
+      <c r="F10">
+        <v>2.1968</v>
+      </c>
+      <c r="G10">
+        <v>2.72</v>
+      </c>
+      <c r="H10">
+        <v>25</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2.8</v>
+      </c>
+      <c r="K10">
+        <v>1.57</v>
+      </c>
+      <c r="L10">
+        <v>1.23</v>
+      </c>
+      <c r="M10">
+        <v>0.10390864</v>
+      </c>
+      <c r="N10">
+        <v>1.12609136</v>
+      </c>
+      <c r="O10">
+        <v>0.2815228399999999</v>
+      </c>
+      <c r="P10">
+        <v>0.8445685199999998</v>
+      </c>
+      <c r="Q10">
+        <v>2.41456852</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1382843451982521</v>
+      </c>
+      <c r="T10">
+        <v>1.431673124685177</v>
+      </c>
+      <c r="U10">
+        <v>0.0473</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.035475</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>11.83732170876262</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1297928639150899</v>
+      </c>
+      <c r="C11">
+        <v>25.12559057995548</v>
+      </c>
+      <c r="D11">
+        <v>24.87699057995548</v>
+      </c>
+      <c r="E11">
+        <v>0.01140000000000008</v>
+      </c>
+      <c r="F11">
+        <v>2.4714</v>
+      </c>
+      <c r="G11">
+        <v>2.72</v>
+      </c>
+      <c r="H11">
+        <v>25</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2.8</v>
+      </c>
+      <c r="K11">
+        <v>1.57</v>
+      </c>
+      <c r="L11">
+        <v>1.23</v>
+      </c>
+      <c r="M11">
+        <v>0.11689722</v>
+      </c>
+      <c r="N11">
+        <v>1.11310278</v>
+      </c>
+      <c r="O11">
+        <v>0.2782756949999999</v>
+      </c>
+      <c r="P11">
+        <v>0.8348270849999998</v>
+      </c>
+      <c r="Q11">
+        <v>2.404827085</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1391210043022966</v>
+      </c>
+      <c r="T11">
+        <v>1.443713434659542</v>
+      </c>
+      <c r="U11">
+        <v>0.0473</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.035475</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>10.52206374112233</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1298111302477879</v>
+      </c>
+      <c r="C12">
+        <v>24.84599765892241</v>
+      </c>
+      <c r="D12">
+        <v>24.87199765892241</v>
+      </c>
+      <c r="E12">
+        <v>0.2860000000000005</v>
+      </c>
+      <c r="F12">
+        <v>2.746</v>
+      </c>
+      <c r="G12">
+        <v>2.72</v>
+      </c>
+      <c r="H12">
+        <v>25</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>2.8</v>
+      </c>
+      <c r="K12">
+        <v>1.57</v>
+      </c>
+      <c r="L12">
+        <v>1.23</v>
+      </c>
+      <c r="M12">
+        <v>0.1403206</v>
+      </c>
+      <c r="N12">
+        <v>1.0896794</v>
+      </c>
+      <c r="O12">
+        <v>0.2724198499999999</v>
+      </c>
+      <c r="P12">
+        <v>0.8172595499999997</v>
+      </c>
+      <c r="Q12">
+        <v>2.38725955</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1399762558308754</v>
+      </c>
+      <c r="T12">
+        <v>1.456021307077782</v>
+      </c>
+      <c r="U12">
+        <v>0.0511</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.038325</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>8.765640967897795</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1295728965804858</v>
+      </c>
+      <c r="C13">
+        <v>24.63667427164081</v>
+      </c>
+      <c r="D13">
+        <v>24.93727427164082</v>
+      </c>
+      <c r="E13">
+        <v>0.5606</v>
+      </c>
+      <c r="F13">
+        <v>3.0206</v>
+      </c>
+      <c r="G13">
+        <v>2.72</v>
+      </c>
+      <c r="H13">
+        <v>25</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2.8</v>
+      </c>
+      <c r="K13">
+        <v>1.57</v>
+      </c>
+      <c r="L13">
+        <v>1.23</v>
+      </c>
+      <c r="M13">
+        <v>0.15435266</v>
+      </c>
+      <c r="N13">
+        <v>1.07564734</v>
+      </c>
+      <c r="O13">
+        <v>0.2689118349999999</v>
+      </c>
+      <c r="P13">
+        <v>0.8067355049999998</v>
+      </c>
+      <c r="Q13">
+        <v>2.376735505</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1408507264949279</v>
+      </c>
+      <c r="T13">
+        <v>1.468605760898679</v>
+      </c>
+      <c r="U13">
+        <v>0.0511</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.038325</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>7.968764516270725</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1295056629131839</v>
+      </c>
+      <c r="C14">
+        <v>24.38055850237074</v>
+      </c>
+      <c r="D14">
+        <v>24.95575850237074</v>
+      </c>
+      <c r="E14">
+        <v>0.8351999999999999</v>
+      </c>
+      <c r="F14">
+        <v>3.2952</v>
+      </c>
+      <c r="G14">
+        <v>2.72</v>
+      </c>
+      <c r="H14">
+        <v>25</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2.8</v>
+      </c>
+      <c r="K14">
+        <v>1.57</v>
+      </c>
+      <c r="L14">
+        <v>1.23</v>
+      </c>
+      <c r="M14">
+        <v>0.1746456</v>
+      </c>
+      <c r="N14">
+        <v>1.0553544</v>
+      </c>
+      <c r="O14">
+        <v>0.2638385999999999</v>
+      </c>
+      <c r="P14">
+        <v>0.7915157999999998</v>
+      </c>
+      <c r="Q14">
+        <v>2.3615158</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1417450714922544</v>
+      </c>
+      <c r="T14">
+        <v>1.481476225033687</v>
+      </c>
+      <c r="U14">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>7.042834173892727</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1292816792458818</v>
+      </c>
+      <c r="C15">
+        <v>24.16773545386249</v>
+      </c>
+      <c r="D15">
+        <v>25.01753545386249</v>
+      </c>
+      <c r="E15">
+        <v>1.1098</v>
+      </c>
+      <c r="F15">
+        <v>3.5698</v>
+      </c>
+      <c r="G15">
+        <v>2.72</v>
+      </c>
+      <c r="H15">
+        <v>25</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2.8</v>
+      </c>
+      <c r="K15">
+        <v>1.57</v>
+      </c>
+      <c r="L15">
+        <v>1.23</v>
+      </c>
+      <c r="M15">
+        <v>0.1891994</v>
+      </c>
+      <c r="N15">
+        <v>1.0408006</v>
+      </c>
+      <c r="O15">
+        <v>0.2602001499999999</v>
+      </c>
+      <c r="P15">
+        <v>0.7806004499999997</v>
+      </c>
+      <c r="Q15">
+        <v>2.35060045</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1426599761446918</v>
+      </c>
+      <c r="T15">
+        <v>1.494642561907431</v>
+      </c>
+      <c r="U15">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>6.501077698977901</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1292676955785798</v>
+      </c>
+      <c r="C16">
+        <v>23.8970024352227</v>
+      </c>
+      <c r="D16">
+        <v>25.0214024352227</v>
+      </c>
+      <c r="E16">
+        <v>1.384400000000001</v>
+      </c>
+      <c r="F16">
+        <v>3.844400000000001</v>
+      </c>
+      <c r="G16">
+        <v>2.72</v>
+      </c>
+      <c r="H16">
+        <v>25</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2.8</v>
+      </c>
+      <c r="K16">
+        <v>1.57</v>
+      </c>
+      <c r="L16">
+        <v>1.23</v>
+      </c>
+      <c r="M16">
+        <v>0.211442</v>
+      </c>
+      <c r="N16">
+        <v>1.018558</v>
+      </c>
+      <c r="O16">
+        <v>0.2546394999999999</v>
+      </c>
+      <c r="P16">
+        <v>0.7639184999999997</v>
+      </c>
+      <c r="Q16">
+        <v>2.3339185</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1435961576495114</v>
+      </c>
+      <c r="T16">
+        <v>1.50811509266196</v>
+      </c>
+      <c r="U16">
+        <v>0.055</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.04125</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.817198096877628</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1290587119112778</v>
+      </c>
+      <c r="C17">
+        <v>23.68033661499575</v>
+      </c>
+      <c r="D17">
+        <v>25.07933661499575</v>
+      </c>
+      <c r="E17">
+        <v>1.659</v>
+      </c>
+      <c r="F17">
+        <v>4.119</v>
+      </c>
+      <c r="G17">
+        <v>2.72</v>
+      </c>
+      <c r="H17">
+        <v>25</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2.8</v>
+      </c>
+      <c r="K17">
+        <v>1.57</v>
+      </c>
+      <c r="L17">
+        <v>1.23</v>
+      </c>
+      <c r="M17">
+        <v>0.226545</v>
+      </c>
+      <c r="N17">
+        <v>1.003455</v>
+      </c>
+      <c r="O17">
+        <v>0.2508637499999999</v>
+      </c>
+      <c r="P17">
+        <v>0.7525912499999998</v>
+      </c>
+      <c r="Q17">
+        <v>2.32259125</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1445543669544445</v>
+      </c>
+      <c r="T17">
+        <v>1.521904624140125</v>
+      </c>
+      <c r="U17">
+        <v>0.055</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.04125</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.429384890419121</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1288497282439758</v>
+      </c>
+      <c r="C18">
+        <v>23.46393969724275</v>
+      </c>
+      <c r="D18">
+        <v>25.13753969724275</v>
+      </c>
+      <c r="E18">
+        <v>1.9336</v>
+      </c>
+      <c r="F18">
+        <v>4.3936</v>
+      </c>
+      <c r="G18">
+        <v>2.72</v>
+      </c>
+      <c r="H18">
+        <v>25</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2.8</v>
+      </c>
+      <c r="K18">
+        <v>1.57</v>
+      </c>
+      <c r="L18">
+        <v>1.23</v>
+      </c>
+      <c r="M18">
+        <v>0.241648</v>
+      </c>
+      <c r="N18">
+        <v>0.9883519999999998</v>
+      </c>
+      <c r="O18">
+        <v>0.2470879999999999</v>
+      </c>
+      <c r="P18">
+        <v>0.7412639999999998</v>
+      </c>
+      <c r="Q18">
+        <v>2.311264</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1455353907666378</v>
+      </c>
+      <c r="T18">
+        <v>1.536022477796341</v>
+      </c>
+      <c r="U18">
+        <v>0.055</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.04125</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.090048334767926</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1286407445766738</v>
+      </c>
+      <c r="C19">
+        <v>23.2478135584917</v>
+      </c>
+      <c r="D19">
+        <v>25.1960135584917</v>
+      </c>
+      <c r="E19">
+        <v>2.208200000000001</v>
+      </c>
+      <c r="F19">
+        <v>4.668200000000001</v>
+      </c>
+      <c r="G19">
+        <v>2.72</v>
+      </c>
+      <c r="H19">
+        <v>25</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2.8</v>
+      </c>
+      <c r="K19">
+        <v>1.57</v>
+      </c>
+      <c r="L19">
+        <v>1.23</v>
+      </c>
+      <c r="M19">
+        <v>0.256751</v>
+      </c>
+      <c r="N19">
+        <v>0.9732489999999998</v>
+      </c>
+      <c r="O19">
+        <v>0.24331225</v>
+      </c>
+      <c r="P19">
+        <v>0.7299367499999998</v>
+      </c>
+      <c r="Q19">
+        <v>2.29993675</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1465400537068359</v>
+      </c>
+      <c r="T19">
+        <v>1.550480520697286</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.04125</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.790633726840401</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1284317609093717</v>
+      </c>
+      <c r="C20">
+        <v>23.03196009277178</v>
+      </c>
+      <c r="D20">
+        <v>25.25476009277178</v>
+      </c>
+      <c r="E20">
+        <v>2.4828</v>
+      </c>
+      <c r="F20">
+        <v>4.9428</v>
+      </c>
+      <c r="G20">
+        <v>2.72</v>
+      </c>
+      <c r="H20">
+        <v>25</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2.8</v>
+      </c>
+      <c r="K20">
+        <v>1.57</v>
+      </c>
+      <c r="L20">
+        <v>1.23</v>
+      </c>
+      <c r="M20">
+        <v>0.271854</v>
+      </c>
+      <c r="N20">
+        <v>0.9581459999999997</v>
+      </c>
+      <c r="O20">
+        <v>0.2395364999999999</v>
+      </c>
+      <c r="P20">
+        <v>0.7186094999999998</v>
+      </c>
+      <c r="Q20">
+        <v>2.2886095</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.147569220621185</v>
+      </c>
+      <c r="T20">
+        <v>1.565291198790936</v>
+      </c>
+      <c r="U20">
+        <v>0.055</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.04125</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.524487408682601</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1287642772420697</v>
+      </c>
+      <c r="C21">
+        <v>22.66401615152473</v>
+      </c>
+      <c r="D21">
+        <v>25.16141615152473</v>
+      </c>
+      <c r="E21">
+        <v>2.757400000000001</v>
+      </c>
+      <c r="F21">
+        <v>5.2174</v>
+      </c>
+      <c r="G21">
+        <v>2.72</v>
+      </c>
+      <c r="H21">
+        <v>25</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2.8</v>
+      </c>
+      <c r="K21">
+        <v>1.57</v>
+      </c>
+      <c r="L21">
+        <v>1.23</v>
+      </c>
+      <c r="M21">
+        <v>0.3067831200000001</v>
+      </c>
+      <c r="N21">
+        <v>0.9232168799999997</v>
+      </c>
+      <c r="O21">
+        <v>0.2308042199999999</v>
+      </c>
+      <c r="P21">
+        <v>0.6924126599999998</v>
+      </c>
+      <c r="Q21">
+        <v>2.26241266</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1486237990642836</v>
+      </c>
+      <c r="T21">
+        <v>1.580467572639986</v>
+      </c>
+      <c r="U21">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.0441</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.009347059251498</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1292137935747677</v>
+      </c>
+      <c r="C22">
+        <v>22.26431944817086</v>
+      </c>
+      <c r="D22">
+        <v>25.03631944817086</v>
+      </c>
+      <c r="E22">
+        <v>3.032000000000001</v>
+      </c>
+      <c r="F22">
+        <v>5.492000000000001</v>
+      </c>
+      <c r="G22">
+        <v>2.72</v>
+      </c>
+      <c r="H22">
+        <v>25</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2.8</v>
+      </c>
+      <c r="K22">
+        <v>1.57</v>
+      </c>
+      <c r="L22">
+        <v>1.23</v>
+      </c>
+      <c r="M22">
+        <v>0.3459960000000001</v>
+      </c>
+      <c r="N22">
+        <v>0.8840039999999997</v>
+      </c>
+      <c r="O22">
+        <v>0.2210009999999999</v>
+      </c>
+      <c r="P22">
+        <v>0.6630029999999998</v>
+      </c>
+      <c r="Q22">
+        <v>2.233003</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1497047419684596</v>
+      </c>
+      <c r="T22">
+        <v>1.596023355835261</v>
+      </c>
+      <c r="U22">
+        <v>0.063</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.04725</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>3.554954392536328</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1301830599074656</v>
+      </c>
+      <c r="C23">
+        <v>21.72416846355341</v>
+      </c>
+      <c r="D23">
+        <v>24.77076846355341</v>
+      </c>
+      <c r="E23">
+        <v>3.3066</v>
+      </c>
+      <c r="F23">
+        <v>5.7666</v>
+      </c>
+      <c r="G23">
+        <v>2.72</v>
+      </c>
+      <c r="H23">
+        <v>25</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2.8</v>
+      </c>
+      <c r="K23">
+        <v>1.57</v>
+      </c>
+      <c r="L23">
+        <v>1.23</v>
+      </c>
+      <c r="M23">
+        <v>0.40423866</v>
+      </c>
+      <c r="N23">
+        <v>0.8257613399999997</v>
+      </c>
+      <c r="O23">
+        <v>0.2064403349999999</v>
+      </c>
+      <c r="P23">
+        <v>0.6193210049999998</v>
+      </c>
+      <c r="Q23">
+        <v>2.189321005</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1508130505157793</v>
+      </c>
+      <c r="T23">
+        <v>1.611972956326619</v>
+      </c>
+      <c r="U23">
+        <v>0.0701</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.052575</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>3.042756969360624</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1336018262401636</v>
+      </c>
+      <c r="C24">
+        <v>20.55627903425784</v>
+      </c>
+      <c r="D24">
+        <v>23.87747903425784</v>
+      </c>
+      <c r="E24">
+        <v>3.5812</v>
+      </c>
+      <c r="F24">
+        <v>6.0412</v>
+      </c>
+      <c r="G24">
+        <v>2.72</v>
+      </c>
+      <c r="H24">
+        <v>25</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2.8</v>
+      </c>
+      <c r="K24">
+        <v>1.57</v>
+      </c>
+      <c r="L24">
+        <v>1.23</v>
+      </c>
+      <c r="M24">
+        <v>0.55216568</v>
+      </c>
+      <c r="N24">
+        <v>0.6778343199999998</v>
+      </c>
+      <c r="O24">
+        <v>0.1694585799999999</v>
+      </c>
+      <c r="P24">
+        <v>0.5083757399999999</v>
+      </c>
+      <c r="Q24">
+        <v>2.07837574</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.151949777230979</v>
+      </c>
+      <c r="T24">
+        <v>1.628331520933141</v>
+      </c>
+      <c r="U24">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.06855</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>2.227592269045044</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1336658425728616</v>
+      </c>
+      <c r="C25">
+        <v>20.26556629440976</v>
+      </c>
+      <c r="D25">
+        <v>23.86136629440976</v>
+      </c>
+      <c r="E25">
+        <v>3.8558</v>
+      </c>
+      <c r="F25">
+        <v>6.3158</v>
+      </c>
+      <c r="G25">
+        <v>2.72</v>
+      </c>
+      <c r="H25">
+        <v>25</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2.8</v>
+      </c>
+      <c r="K25">
+        <v>1.57</v>
+      </c>
+      <c r="L25">
+        <v>1.23</v>
+      </c>
+      <c r="M25">
+        <v>0.57726412</v>
+      </c>
+      <c r="N25">
+        <v>0.6527358799999997</v>
+      </c>
+      <c r="O25">
+        <v>0.1631839699999999</v>
+      </c>
+      <c r="P25">
+        <v>0.4895519099999998</v>
+      </c>
+      <c r="Q25">
+        <v>2.05955191</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1531160293154047</v>
+      </c>
+      <c r="T25">
+        <v>1.64511498332165</v>
+      </c>
+      <c r="U25">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.06855</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>2.130740431260477</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1337298589055596</v>
+      </c>
+      <c r="C26">
+        <v>19.97487528594369</v>
+      </c>
+      <c r="D26">
+        <v>23.84527528594369</v>
+      </c>
+      <c r="E26">
+        <v>4.1304</v>
+      </c>
+      <c r="F26">
+        <v>6.5904</v>
+      </c>
+      <c r="G26">
+        <v>2.72</v>
+      </c>
+      <c r="H26">
+        <v>25</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2.8</v>
+      </c>
+      <c r="K26">
+        <v>1.57</v>
+      </c>
+      <c r="L26">
+        <v>1.23</v>
+      </c>
+      <c r="M26">
+        <v>0.60236256</v>
+      </c>
+      <c r="N26">
+        <v>0.6276374399999998</v>
+      </c>
+      <c r="O26">
+        <v>0.1569093599999999</v>
+      </c>
+      <c r="P26">
+        <v>0.4707280799999998</v>
+      </c>
+      <c r="Q26">
+        <v>2.04072808</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1543129722441574</v>
+      </c>
+      <c r="T26">
+        <v>1.662340115773014</v>
+      </c>
+      <c r="U26">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.06855</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.041959579957957</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1377501252382576</v>
+      </c>
+      <c r="C27">
+        <v>18.7314603683762</v>
+      </c>
+      <c r="D27">
+        <v>22.87646036837621</v>
+      </c>
+      <c r="E27">
+        <v>4.405</v>
+      </c>
+      <c r="F27">
+        <v>6.865</v>
+      </c>
+      <c r="G27">
+        <v>2.72</v>
+      </c>
+      <c r="H27">
+        <v>25</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2.8</v>
+      </c>
+      <c r="K27">
+        <v>1.57</v>
+      </c>
+      <c r="L27">
+        <v>1.23</v>
+      </c>
+      <c r="M27">
+        <v>0.7723125000000001</v>
+      </c>
+      <c r="N27">
+        <v>0.4576874999999997</v>
+      </c>
+      <c r="O27">
+        <v>0.1144218749999999</v>
+      </c>
+      <c r="P27">
+        <v>0.3432656249999998</v>
+      </c>
+      <c r="Q27">
+        <v>1.913265625</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1555418336510101</v>
+      </c>
+      <c r="T27">
+        <v>1.680024585089749</v>
+      </c>
+      <c r="U27">
+        <v>0.1125</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>1.592619567856275</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1379723915709556</v>
+      </c>
+      <c r="C28">
+        <v>18.40558937580816</v>
+      </c>
+      <c r="D28">
+        <v>22.82518937580816</v>
+      </c>
+      <c r="E28">
+        <v>4.679600000000001</v>
+      </c>
+      <c r="F28">
+        <v>7.139600000000001</v>
+      </c>
+      <c r="G28">
+        <v>2.72</v>
+      </c>
+      <c r="H28">
+        <v>25</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2.8</v>
+      </c>
+      <c r="K28">
+        <v>1.57</v>
+      </c>
+      <c r="L28">
+        <v>1.23</v>
+      </c>
+      <c r="M28">
+        <v>0.8032050000000001</v>
+      </c>
+      <c r="N28">
+        <v>0.4267949999999997</v>
+      </c>
+      <c r="O28">
+        <v>0.1066987499999999</v>
+      </c>
+      <c r="P28">
+        <v>0.3200962499999997</v>
+      </c>
+      <c r="Q28">
+        <v>1.89009625</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1568039075283184</v>
+      </c>
+      <c r="T28">
+        <v>1.698187013036665</v>
+      </c>
+      <c r="U28">
+        <v>0.1125</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>1.531364969092572</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1582817778085678</v>
+      </c>
+      <c r="C29">
+        <v>14.25118782378699</v>
+      </c>
+      <c r="D29">
+        <v>18.94538782378699</v>
+      </c>
+      <c r="E29">
+        <v>4.954200000000001</v>
+      </c>
+      <c r="F29">
+        <v>7.414200000000001</v>
+      </c>
+      <c r="G29">
+        <v>2.72</v>
+      </c>
+      <c r="H29">
+        <v>25</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2.8</v>
+      </c>
+      <c r="K29">
+        <v>1.57</v>
+      </c>
+      <c r="L29">
+        <v>1.23</v>
+      </c>
+      <c r="M29">
+        <v>1.45763172</v>
+      </c>
+      <c r="N29">
+        <v>-0.2276317200000004</v>
+      </c>
+      <c r="O29">
+        <v>-0.05690793000000011</v>
+      </c>
+      <c r="P29">
+        <v>-0.1707237900000003</v>
+      </c>
+      <c r="Q29">
+        <v>1.39927621</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1594491563630921</v>
+      </c>
+      <c r="T29">
+        <v>1.736254627165334</v>
+      </c>
+      <c r="U29">
+        <v>0.1966</v>
+      </c>
+      <c r="V29">
+        <v>0.2109586363831324</v>
+      </c>
+      <c r="W29">
+        <v>0.1551255320870762</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.8438345455325297</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1598597778085678</v>
+      </c>
+      <c r="C30">
+        <v>13.72963691633355</v>
+      </c>
+      <c r="D30">
+        <v>18.69843691633356</v>
+      </c>
+      <c r="E30">
+        <v>5.228800000000001</v>
+      </c>
+      <c r="F30">
+        <v>7.688800000000001</v>
+      </c>
+      <c r="G30">
+        <v>2.72</v>
+      </c>
+      <c r="H30">
+        <v>25</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2.8</v>
+      </c>
+      <c r="K30">
+        <v>1.57</v>
+      </c>
+      <c r="L30">
+        <v>1.23</v>
+      </c>
+      <c r="M30">
+        <v>1.51161808</v>
+      </c>
+      <c r="N30">
+        <v>-0.2816180800000005</v>
+      </c>
+      <c r="O30">
+        <v>-0.07040452000000014</v>
+      </c>
+      <c r="P30">
+        <v>-0.2112135600000004</v>
+      </c>
+      <c r="Q30">
+        <v>1.35878644</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1611248390903573</v>
+      </c>
+      <c r="T30">
+        <v>1.760369274764853</v>
+      </c>
+      <c r="U30">
+        <v>0.1966</v>
+      </c>
+      <c r="V30">
+        <v>0.2034243993694491</v>
+      </c>
+      <c r="W30">
+        <v>0.1566067630839663</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.8136975974777965</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1668537330178424</v>
+      </c>
+      <c r="C31">
+        <v>12.43377789331029</v>
+      </c>
+      <c r="D31">
+        <v>17.67717789331029</v>
+      </c>
+      <c r="E31">
+        <v>5.5034</v>
+      </c>
+      <c r="F31">
+        <v>7.9634</v>
+      </c>
+      <c r="G31">
+        <v>2.72</v>
+      </c>
+      <c r="H31">
+        <v>25</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2.8</v>
+      </c>
+      <c r="K31">
+        <v>1.57</v>
+      </c>
+      <c r="L31">
+        <v>1.23</v>
+      </c>
+      <c r="M31">
+        <v>1.70257492</v>
+      </c>
+      <c r="N31">
+        <v>-0.4725749200000002</v>
+      </c>
+      <c r="O31">
+        <v>-0.1181437300000001</v>
+      </c>
+      <c r="P31">
+        <v>-0.3544311900000002</v>
+      </c>
+      <c r="Q31">
+        <v>1.21556881</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1634504779638477</v>
+      </c>
+      <c r="T31">
+        <v>1.793837401496392</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.1806087922404025</v>
+      </c>
+      <c r="W31">
+        <v>0.1751858402190019</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.7224351689616101</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1686037330178424</v>
+      </c>
+      <c r="C32">
+        <v>11.9208560777964</v>
+      </c>
+      <c r="D32">
+        <v>17.4388560777964</v>
+      </c>
+      <c r="E32">
+        <v>5.778</v>
+      </c>
+      <c r="F32">
+        <v>8.238</v>
+      </c>
+      <c r="G32">
+        <v>2.72</v>
+      </c>
+      <c r="H32">
+        <v>25</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2.8</v>
+      </c>
+      <c r="K32">
+        <v>1.57</v>
+      </c>
+      <c r="L32">
+        <v>1.23</v>
+      </c>
+      <c r="M32">
+        <v>1.7612844</v>
+      </c>
+      <c r="N32">
+        <v>-0.5312844000000001</v>
+      </c>
+      <c r="O32">
+        <v>-0.1328211</v>
+      </c>
+      <c r="P32">
+        <v>-0.3984633000000001</v>
+      </c>
+      <c r="Q32">
+        <v>1.1715367</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1652311990776169</v>
+      </c>
+      <c r="T32">
+        <v>1.819463650089198</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0.1745884991657224</v>
+      </c>
+      <c r="W32">
+        <v>0.1764729788783685</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.6983539966628898</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1703537330178424</v>
+      </c>
+      <c r="C33">
+        <v>11.41427483761369</v>
+      </c>
+      <c r="D33">
+        <v>17.20687483761369</v>
+      </c>
+      <c r="E33">
+        <v>6.052600000000001</v>
+      </c>
+      <c r="F33">
+        <v>8.512600000000001</v>
+      </c>
+      <c r="G33">
+        <v>2.72</v>
+      </c>
+      <c r="H33">
+        <v>25</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>2.8</v>
+      </c>
+      <c r="K33">
+        <v>1.57</v>
+      </c>
+      <c r="L33">
+        <v>1.23</v>
+      </c>
+      <c r="M33">
+        <v>1.81999388</v>
+      </c>
+      <c r="N33">
+        <v>-0.5899938800000004</v>
+      </c>
+      <c r="O33">
+        <v>-0.1474984700000001</v>
+      </c>
+      <c r="P33">
+        <v>-0.4424954100000003</v>
+      </c>
+      <c r="Q33">
+        <v>1.12750459</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1670635352961331</v>
+      </c>
+      <c r="T33">
+        <v>1.845832688496288</v>
+      </c>
+      <c r="U33">
+        <v>0.2138</v>
+      </c>
+      <c r="V33">
+        <v>0.1689566120958604</v>
+      </c>
+      <c r="W33">
+        <v>0.177677076333905</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.6758264483834416</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1721037330178424</v>
+      </c>
+      <c r="C34">
+        <v>10.91378445717106</v>
+      </c>
+      <c r="D34">
+        <v>16.98098445717106</v>
+      </c>
+      <c r="E34">
+        <v>6.3272</v>
+      </c>
+      <c r="F34">
+        <v>8.7872</v>
+      </c>
+      <c r="G34">
+        <v>2.72</v>
+      </c>
+      <c r="H34">
+        <v>25</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>2.8</v>
+      </c>
+      <c r="K34">
+        <v>1.57</v>
+      </c>
+      <c r="L34">
+        <v>1.23</v>
+      </c>
+      <c r="M34">
+        <v>1.87870336</v>
+      </c>
+      <c r="N34">
+        <v>-0.6487033600000003</v>
+      </c>
+      <c r="O34">
+        <v>-0.1621758400000001</v>
+      </c>
+      <c r="P34">
+        <v>-0.4865275200000002</v>
+      </c>
+      <c r="Q34">
+        <v>1.08347248</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1689497637563704</v>
+      </c>
+      <c r="T34">
+        <v>1.872977286856527</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.1636767179678648</v>
+      </c>
+      <c r="W34">
+        <v>0.1788059176984705</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.654706871871459</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1738537330178424</v>
+      </c>
+      <c r="C35">
+        <v>10.41914816394158</v>
+      </c>
+      <c r="D35">
+        <v>16.76094816394158</v>
+      </c>
+      <c r="E35">
+        <v>6.6018</v>
+      </c>
+      <c r="F35">
+        <v>9.0618</v>
+      </c>
+      <c r="G35">
+        <v>2.72</v>
+      </c>
+      <c r="H35">
+        <v>25</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2.8</v>
+      </c>
+      <c r="K35">
+        <v>1.57</v>
+      </c>
+      <c r="L35">
+        <v>1.23</v>
+      </c>
+      <c r="M35">
+        <v>1.93741284</v>
+      </c>
+      <c r="N35">
+        <v>-0.7074128400000002</v>
+      </c>
+      <c r="O35">
+        <v>-0.17685321</v>
+      </c>
+      <c r="P35">
+        <v>-0.5305596300000002</v>
+      </c>
+      <c r="Q35">
+        <v>1.03944037</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1708922975437789</v>
+      </c>
+      <c r="T35">
+        <v>1.900932171734983</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.158716817423384</v>
+      </c>
+      <c r="W35">
+        <v>0.1798663444348805</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.6348672696935361</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1756037330178424</v>
+      </c>
+      <c r="C36">
+        <v>9.930141300621024</v>
+      </c>
+      <c r="D36">
+        <v>16.54654130062103</v>
+      </c>
+      <c r="E36">
+        <v>6.876400000000001</v>
+      </c>
+      <c r="F36">
+        <v>9.336400000000001</v>
+      </c>
+      <c r="G36">
+        <v>2.72</v>
+      </c>
+      <c r="H36">
+        <v>25</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2.8</v>
+      </c>
+      <c r="K36">
+        <v>1.57</v>
+      </c>
+      <c r="L36">
+        <v>1.23</v>
+      </c>
+      <c r="M36">
+        <v>1.99612232</v>
+      </c>
+      <c r="N36">
+        <v>-0.7661223200000005</v>
+      </c>
+      <c r="O36">
+        <v>-0.1915305800000001</v>
+      </c>
+      <c r="P36">
+        <v>-0.5745917400000004</v>
+      </c>
+      <c r="Q36">
+        <v>0.9954082599999997</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1728936959914119</v>
+      </c>
+      <c r="T36">
+        <v>1.929734174337028</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.154048675734461</v>
+      </c>
+      <c r="W36">
+        <v>0.1808643931279722</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.6161947029378438</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1773537330178424</v>
+      </c>
+      <c r="C37">
+        <v>9.446550560022523</v>
+      </c>
+      <c r="D37">
+        <v>16.33755056002252</v>
+      </c>
+      <c r="E37">
+        <v>7.151000000000001</v>
+      </c>
+      <c r="F37">
+        <v>9.611000000000001</v>
+      </c>
+      <c r="G37">
+        <v>2.72</v>
+      </c>
+      <c r="H37">
+        <v>25</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2.8</v>
+      </c>
+      <c r="K37">
+        <v>1.57</v>
+      </c>
+      <c r="L37">
+        <v>1.23</v>
+      </c>
+      <c r="M37">
+        <v>2.0548318</v>
+      </c>
+      <c r="N37">
+        <v>-0.8248318000000003</v>
+      </c>
+      <c r="O37">
+        <v>-0.2062079500000001</v>
+      </c>
+      <c r="P37">
+        <v>-0.6186238500000003</v>
+      </c>
+      <c r="Q37">
+        <v>0.9513761499999998</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1749566759297413</v>
+      </c>
+      <c r="T37">
+        <v>1.959422392403752</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1496472849991906</v>
+      </c>
+      <c r="W37">
+        <v>0.181805410467173</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.5985891399967627</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1791037330178424</v>
+      </c>
+      <c r="C38">
+        <v>8.968173277229884</v>
+      </c>
+      <c r="D38">
+        <v>16.13377327722988</v>
+      </c>
+      <c r="E38">
+        <v>7.4256</v>
+      </c>
+      <c r="F38">
+        <v>9.8856</v>
+      </c>
+      <c r="G38">
+        <v>2.72</v>
+      </c>
+      <c r="H38">
+        <v>25</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2.8</v>
+      </c>
+      <c r="K38">
+        <v>1.57</v>
+      </c>
+      <c r="L38">
+        <v>1.23</v>
+      </c>
+      <c r="M38">
+        <v>2.11354128</v>
+      </c>
+      <c r="N38">
+        <v>-0.88354128</v>
+      </c>
+      <c r="O38">
+        <v>-0.22088532</v>
+      </c>
+      <c r="P38">
+        <v>-0.6626559599999999</v>
+      </c>
+      <c r="Q38">
+        <v>0.9073440400000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1770841239911435</v>
+      </c>
+      <c r="T38">
+        <v>1.99003836728506</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1454904159714354</v>
+      </c>
+      <c r="W38">
+        <v>0.1826941490653071</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.5819616638857414</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1808537330178424</v>
+      </c>
+      <c r="C39">
+        <v>8.494816774071985</v>
+      </c>
+      <c r="D39">
+        <v>15.93501677407199</v>
+      </c>
+      <c r="E39">
+        <v>7.7002</v>
+      </c>
+      <c r="F39">
+        <v>10.1602</v>
+      </c>
+      <c r="G39">
+        <v>2.72</v>
+      </c>
+      <c r="H39">
+        <v>25</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2.8</v>
+      </c>
+      <c r="K39">
+        <v>1.57</v>
+      </c>
+      <c r="L39">
+        <v>1.23</v>
+      </c>
+      <c r="M39">
+        <v>2.17225076</v>
+      </c>
+      <c r="N39">
+        <v>-0.9422507600000001</v>
+      </c>
+      <c r="O39">
+        <v>-0.23556269</v>
+      </c>
+      <c r="P39">
+        <v>-0.70668807</v>
+      </c>
+      <c r="Q39">
+        <v>0.8633119300000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.179279110086241</v>
+      </c>
+      <c r="T39">
+        <v>2.021626277876886</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.141558242566802</v>
+      </c>
+      <c r="W39">
+        <v>0.1835348477392177</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.566232970267208</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1826037330178424</v>
+      </c>
+      <c r="C40">
+        <v>8.026297751461032</v>
+      </c>
+      <c r="D40">
+        <v>15.74109775146103</v>
+      </c>
+      <c r="E40">
+        <v>7.974800000000001</v>
+      </c>
+      <c r="F40">
+        <v>10.4348</v>
+      </c>
+      <c r="G40">
+        <v>2.72</v>
+      </c>
+      <c r="H40">
+        <v>25</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2.8</v>
+      </c>
+      <c r="K40">
+        <v>1.57</v>
+      </c>
+      <c r="L40">
+        <v>1.23</v>
+      </c>
+      <c r="M40">
+        <v>2.23096024</v>
+      </c>
+      <c r="N40">
+        <v>-1.00096024</v>
+      </c>
+      <c r="O40">
+        <v>-0.25024006</v>
+      </c>
+      <c r="P40">
+        <v>-0.7507201800000001</v>
+      </c>
+      <c r="Q40">
+        <v>0.81927982</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1815449021844062</v>
+      </c>
+      <c r="T40">
+        <v>2.054233153326514</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.1378330256571493</v>
+      </c>
+      <c r="W40">
+        <v>0.1843312991145015</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.5513321026285971</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1843537330178424</v>
+      </c>
+      <c r="C41">
+        <v>7.562441725566595</v>
+      </c>
+      <c r="D41">
+        <v>15.5518417255666</v>
+      </c>
+      <c r="E41">
+        <v>8.249400000000001</v>
+      </c>
+      <c r="F41">
+        <v>10.7094</v>
+      </c>
+      <c r="G41">
+        <v>2.72</v>
+      </c>
+      <c r="H41">
+        <v>25</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2.8</v>
+      </c>
+      <c r="K41">
+        <v>1.57</v>
+      </c>
+      <c r="L41">
+        <v>1.23</v>
+      </c>
+      <c r="M41">
+        <v>2.28966972</v>
+      </c>
+      <c r="N41">
+        <v>-1.05966972</v>
+      </c>
+      <c r="O41">
+        <v>-0.2649174300000001</v>
+      </c>
+      <c r="P41">
+        <v>-0.7947522900000001</v>
+      </c>
+      <c r="Q41">
+        <v>0.7752477099999999</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.183884982548085</v>
+      </c>
+      <c r="T41">
+        <v>2.087909106659736</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.1342988455120942</v>
+      </c>
+      <c r="W41">
+        <v>0.1850869068295143</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5371953820483768</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1861037330178424</v>
+      </c>
+      <c r="C42">
+        <v>7.103082504179824</v>
+      </c>
+      <c r="D42">
+        <v>15.36708250417983</v>
+      </c>
+      <c r="E42">
+        <v>8.524000000000001</v>
+      </c>
+      <c r="F42">
+        <v>10.984</v>
+      </c>
+      <c r="G42">
+        <v>2.72</v>
+      </c>
+      <c r="H42">
+        <v>25</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2.8</v>
+      </c>
+      <c r="K42">
+        <v>1.57</v>
+      </c>
+      <c r="L42">
+        <v>1.23</v>
+      </c>
+      <c r="M42">
+        <v>2.3483792</v>
+      </c>
+      <c r="N42">
+        <v>-1.1183792</v>
+      </c>
+      <c r="O42">
+        <v>-0.2795948000000001</v>
+      </c>
+      <c r="P42">
+        <v>-0.8387844000000002</v>
+      </c>
+      <c r="Q42">
+        <v>0.7312155999999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1863030655905531</v>
+      </c>
+      <c r="T42">
+        <v>2.122707591770731</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.1309413743742918</v>
+      </c>
+      <c r="W42">
+        <v>0.1858047341587764</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.5237654974971673</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1878537330178424</v>
+      </c>
+      <c r="C43">
+        <v>6.648061699964906</v>
+      </c>
+      <c r="D43">
+        <v>15.18666169996491</v>
+      </c>
+      <c r="E43">
+        <v>8.7986</v>
+      </c>
+      <c r="F43">
+        <v>11.2586</v>
+      </c>
+      <c r="G43">
+        <v>2.72</v>
+      </c>
+      <c r="H43">
+        <v>25</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>2.8</v>
+      </c>
+      <c r="K43">
+        <v>1.57</v>
+      </c>
+      <c r="L43">
+        <v>1.23</v>
+      </c>
+      <c r="M43">
+        <v>2.40708868</v>
+      </c>
+      <c r="N43">
+        <v>-1.17708868</v>
+      </c>
+      <c r="O43">
+        <v>-0.2942721700000001</v>
+      </c>
+      <c r="P43">
+        <v>-0.8828165100000003</v>
+      </c>
+      <c r="Q43">
+        <v>0.6871834899999998</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.188803117549715</v>
+      </c>
+      <c r="T43">
+        <v>2.158685686546506</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.1277476823163823</v>
+      </c>
+      <c r="W43">
+        <v>0.1864875455207575</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.510990729265529</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2006158380813345</v>
+      </c>
+      <c r="C44">
+        <v>5.175718793728215</v>
+      </c>
+      <c r="D44">
+        <v>13.98891879372822</v>
+      </c>
+      <c r="E44">
+        <v>9.0732</v>
+      </c>
+      <c r="F44">
+        <v>11.5332</v>
+      </c>
+      <c r="G44">
+        <v>2.72</v>
+      </c>
+      <c r="H44">
+        <v>25</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>2.8</v>
+      </c>
+      <c r="K44">
+        <v>1.57</v>
+      </c>
+      <c r="L44">
+        <v>1.23</v>
+      </c>
+      <c r="M44">
+        <v>2.75412816</v>
+      </c>
+      <c r="N44">
+        <v>-1.524128160000001</v>
+      </c>
+      <c r="O44">
+        <v>-0.3810320400000002</v>
+      </c>
+      <c r="P44">
+        <v>-1.14309612</v>
+      </c>
+      <c r="Q44">
+        <v>0.4269038799999996</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1922723179617654</v>
+      </c>
+      <c r="T44">
+        <v>2.208610737409348</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.1116505776550354</v>
+      </c>
+      <c r="W44">
+        <v>0.2121378420559775</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.4466023106201418</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2026158380813345</v>
+      </c>
+      <c r="C45">
+        <v>4.730330438248416</v>
+      </c>
+      <c r="D45">
+        <v>13.81813043824842</v>
+      </c>
+      <c r="E45">
+        <v>9.347799999999999</v>
+      </c>
+      <c r="F45">
+        <v>11.8078</v>
+      </c>
+      <c r="G45">
+        <v>2.72</v>
+      </c>
+      <c r="H45">
+        <v>25</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>2.8</v>
+      </c>
+      <c r="K45">
+        <v>1.57</v>
+      </c>
+      <c r="L45">
+        <v>1.23</v>
+      </c>
+      <c r="M45">
+        <v>2.81970264</v>
+      </c>
+      <c r="N45">
+        <v>-1.58970264</v>
+      </c>
+      <c r="O45">
+        <v>-0.3974256600000001</v>
+      </c>
+      <c r="P45">
+        <v>-1.19227698</v>
+      </c>
+      <c r="Q45">
+        <v>0.3777230199999999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1949648147681121</v>
+      </c>
+      <c r="T45">
+        <v>2.247358294206003</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.1090540525932905</v>
+      </c>
+      <c r="W45">
+        <v>0.2127578922407223</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.4362162103731618</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2046158380813345</v>
+      </c>
+      <c r="C46">
+        <v>4.289062035541665</v>
+      </c>
+      <c r="D46">
+        <v>13.65146203554166</v>
+      </c>
+      <c r="E46">
+        <v>9.622399999999999</v>
+      </c>
+      <c r="F46">
+        <v>12.0824</v>
+      </c>
+      <c r="G46">
+        <v>2.72</v>
+      </c>
+      <c r="H46">
+        <v>25</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2.8</v>
+      </c>
+      <c r="K46">
+        <v>1.57</v>
+      </c>
+      <c r="L46">
+        <v>1.23</v>
+      </c>
+      <c r="M46">
+        <v>2.88527712</v>
+      </c>
+      <c r="N46">
+        <v>-1.65527712</v>
+      </c>
+      <c r="O46">
+        <v>-0.4138192800000001</v>
+      </c>
+      <c r="P46">
+        <v>-1.24145784</v>
+      </c>
+      <c r="Q46">
+        <v>0.3285421599999998</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1977534721746856</v>
+      </c>
+      <c r="T46">
+        <v>2.287489692316825</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.1065755513979884</v>
+      </c>
+      <c r="W46">
+        <v>0.2133497583261604</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.4263022055919536</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2066158380813345</v>
+      </c>
+      <c r="C47">
+        <v>3.851766282964066</v>
+      </c>
+      <c r="D47">
+        <v>13.48876628296407</v>
+      </c>
+      <c r="E47">
+        <v>9.897000000000002</v>
+      </c>
+      <c r="F47">
+        <v>12.357</v>
+      </c>
+      <c r="G47">
+        <v>2.72</v>
+      </c>
+      <c r="H47">
+        <v>25</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>2.8</v>
+      </c>
+      <c r="K47">
+        <v>1.57</v>
+      </c>
+      <c r="L47">
+        <v>1.23</v>
+      </c>
+      <c r="M47">
+        <v>2.9508516</v>
+      </c>
+      <c r="N47">
+        <v>-1.720851600000001</v>
+      </c>
+      <c r="O47">
+        <v>-0.4302129000000002</v>
+      </c>
+      <c r="P47">
+        <v>-1.290638700000001</v>
+      </c>
+      <c r="Q47">
+        <v>0.2793612999999995</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2006435353051344</v>
+      </c>
+      <c r="T47">
+        <v>2.329080413995312</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.1042072058113664</v>
+      </c>
+      <c r="W47">
+        <v>0.2139153192522457</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.4168288232454657</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2086158380813345</v>
+      </c>
+      <c r="C48">
+        <v>3.418302817278336</v>
+      </c>
+      <c r="D48">
+        <v>13.32990281727834</v>
+      </c>
+      <c r="E48">
+        <v>10.1716</v>
+      </c>
+      <c r="F48">
+        <v>12.6316</v>
+      </c>
+      <c r="G48">
+        <v>2.72</v>
+      </c>
+      <c r="H48">
+        <v>25</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2.8</v>
+      </c>
+      <c r="K48">
+        <v>1.57</v>
+      </c>
+      <c r="L48">
+        <v>1.23</v>
+      </c>
+      <c r="M48">
+        <v>3.01642608</v>
+      </c>
+      <c r="N48">
+        <v>-1.786426080000001</v>
+      </c>
+      <c r="O48">
+        <v>-0.4466065200000002</v>
+      </c>
+      <c r="P48">
+        <v>-1.33981956</v>
+      </c>
+      <c r="Q48">
+        <v>0.2301804399999996</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.203640637810785</v>
+      </c>
+      <c r="T48">
+        <v>2.372211532773003</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.1019418317719889</v>
+      </c>
+      <c r="W48">
+        <v>0.2144562905728491</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.4077673270879556</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2106158380813345</v>
+      </c>
+      <c r="C49">
+        <v>2.988537810767488</v>
+      </c>
+      <c r="D49">
+        <v>13.17473781076749</v>
+      </c>
+      <c r="E49">
+        <v>10.4462</v>
+      </c>
+      <c r="F49">
+        <v>12.9062</v>
+      </c>
+      <c r="G49">
+        <v>2.72</v>
+      </c>
+      <c r="H49">
+        <v>25</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2.8</v>
+      </c>
+      <c r="K49">
+        <v>1.57</v>
+      </c>
+      <c r="L49">
+        <v>1.23</v>
+      </c>
+      <c r="M49">
+        <v>3.08200056</v>
+      </c>
+      <c r="N49">
+        <v>-1.852000560000001</v>
+      </c>
+      <c r="O49">
+        <v>-0.4630001400000002</v>
+      </c>
+      <c r="P49">
+        <v>-1.389000420000001</v>
+      </c>
+      <c r="Q49">
+        <v>0.1809995799999995</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2067508385241961</v>
+      </c>
+      <c r="T49">
+        <v>2.416970240938532</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.09977285662790401</v>
+      </c>
+      <c r="W49">
+        <v>0.2149742418372565</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3990914265116161</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2126158380813345</v>
+      </c>
+      <c r="C50">
+        <v>2.562343595232278</v>
+      </c>
+      <c r="D50">
+        <v>13.02314359523228</v>
+      </c>
+      <c r="E50">
+        <v>10.7208</v>
+      </c>
+      <c r="F50">
+        <v>13.1808</v>
+      </c>
+      <c r="G50">
+        <v>2.72</v>
+      </c>
+      <c r="H50">
+        <v>25</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>2.8</v>
+      </c>
+      <c r="K50">
+        <v>1.57</v>
+      </c>
+      <c r="L50">
+        <v>1.23</v>
+      </c>
+      <c r="M50">
+        <v>3.14757504</v>
+      </c>
+      <c r="N50">
+        <v>-1.91757504</v>
+      </c>
+      <c r="O50">
+        <v>-0.4793937600000001</v>
+      </c>
+      <c r="P50">
+        <v>-1.43818128</v>
+      </c>
+      <c r="Q50">
+        <v>0.1318187199999998</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2099806623419691</v>
+      </c>
+      <c r="T50">
+        <v>2.463450437879657</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.09769425544815603</v>
+      </c>
+      <c r="W50">
+        <v>0.2154706117989804</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3907770217926241</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2146158380813345</v>
+      </c>
+      <c r="C51">
+        <v>2.139598311651994</v>
+      </c>
+      <c r="D51">
+        <v>12.87499831165199</v>
+      </c>
+      <c r="E51">
+        <v>10.9954</v>
+      </c>
+      <c r="F51">
+        <v>13.4554</v>
+      </c>
+      <c r="G51">
+        <v>2.72</v>
+      </c>
+      <c r="H51">
+        <v>25</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>2.8</v>
+      </c>
+      <c r="K51">
+        <v>1.57</v>
+      </c>
+      <c r="L51">
+        <v>1.23</v>
+      </c>
+      <c r="M51">
+        <v>3.21314952</v>
+      </c>
+      <c r="N51">
+        <v>-1.983149520000001</v>
+      </c>
+      <c r="O51">
+        <v>-0.4957873800000002</v>
+      </c>
+      <c r="P51">
+        <v>-1.487362140000001</v>
+      </c>
+      <c r="Q51">
+        <v>0.08263785999999951</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2133371459173018</v>
+      </c>
+      <c r="T51">
+        <v>2.511753387642004</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.09570049513288753</v>
+      </c>
+      <c r="W51">
+        <v>0.2159467217622665</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3828019805315501</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2166158380813345</v>
+      </c>
+      <c r="C52">
+        <v>1.720185583488121</v>
+      </c>
+      <c r="D52">
+        <v>12.73018558348812</v>
+      </c>
+      <c r="E52">
+        <v>11.27</v>
+      </c>
+      <c r="F52">
+        <v>13.73</v>
+      </c>
+      <c r="G52">
+        <v>2.72</v>
+      </c>
+      <c r="H52">
+        <v>25</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2.8</v>
+      </c>
+      <c r="K52">
+        <v>1.57</v>
+      </c>
+      <c r="L52">
+        <v>1.23</v>
+      </c>
+      <c r="M52">
+        <v>3.278724</v>
+      </c>
+      <c r="N52">
+        <v>-2.048724000000001</v>
+      </c>
+      <c r="O52">
+        <v>-0.5121810000000002</v>
+      </c>
+      <c r="P52">
+        <v>-1.536543000000001</v>
+      </c>
+      <c r="Q52">
+        <v>0.0334569999999994</v>
+      </c>
+      <c r="R52">
         <v>1</v>
       </c>
-      <c r="U3">
-        <v>1.75</v>
-      </c>
-      <c r="V3">
-        <v>0.06272401433691757</v>
-      </c>
-      <c r="W3">
-        <v>0.008673139158576053</v>
-      </c>
-      <c r="X3">
-        <v>0.0755630158999183</v>
-      </c>
-      <c r="Y3">
-        <v>-0.06688987674134225</v>
-      </c>
-      <c r="Z3">
-        <v>0.754257907542579</v>
-      </c>
-      <c r="AA3">
-        <v>-0.004352737278669491</v>
-      </c>
-      <c r="AB3">
-        <v>0.07082949342258638</v>
-      </c>
-      <c r="AC3">
-        <v>-0.07518223070125586</v>
-      </c>
-      <c r="AD3">
-        <v>2.67</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>2.67</v>
-      </c>
-      <c r="AG3">
-        <v>0.9199999999999999</v>
-      </c>
-      <c r="AH3">
-        <v>0.0873405299313052</v>
-      </c>
-      <c r="AI3">
-        <v>0.07527488018043417</v>
-      </c>
-      <c r="AJ3">
-        <v>0.03192227619708535</v>
-      </c>
-      <c r="AK3">
-        <v>0.02728351126927639</v>
-      </c>
-      <c r="AL3">
-        <v>0.068</v>
-      </c>
-      <c r="AM3">
-        <v>-0.724</v>
-      </c>
-      <c r="AN3">
-        <v>3.814285714285715</v>
-      </c>
-      <c r="AO3">
-        <v>-2.279411764705882</v>
-      </c>
-      <c r="AP3">
-        <v>1.314285714285714</v>
-      </c>
-      <c r="AQ3">
-        <v>0.2140883977900553</v>
+      <c r="S52">
+        <v>0.2168278888356479</v>
+      </c>
+      <c r="T52">
+        <v>2.561988455394844</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.09378648523022978</v>
+      </c>
+      <c r="W52">
+        <v>0.2164037873270211</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.375145940920919</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2186158380813345</v>
+      </c>
+      <c r="C53">
+        <v>1.303994211790041</v>
+      </c>
+      <c r="D53">
+        <v>12.58859421179004</v>
+      </c>
+      <c r="E53">
+        <v>11.5446</v>
+      </c>
+      <c r="F53">
+        <v>14.0046</v>
+      </c>
+      <c r="G53">
+        <v>2.72</v>
+      </c>
+      <c r="H53">
+        <v>25</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2.8</v>
+      </c>
+      <c r="K53">
+        <v>1.57</v>
+      </c>
+      <c r="L53">
+        <v>1.23</v>
+      </c>
+      <c r="M53">
+        <v>3.34429848</v>
+      </c>
+      <c r="N53">
+        <v>-2.11429848</v>
+      </c>
+      <c r="O53">
+        <v>-0.5285746200000001</v>
+      </c>
+      <c r="P53">
+        <v>-1.58572386</v>
+      </c>
+      <c r="Q53">
+        <v>-0.01572386000000026</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2204611110567835</v>
+      </c>
+      <c r="T53">
+        <v>2.614273934076371</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.09194753453944098</v>
+      </c>
+      <c r="W53">
+        <v>0.2168429287519815</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3677901381577638</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2206158380813345</v>
+      </c>
+      <c r="C54">
+        <v>0.8909178904240349</v>
+      </c>
+      <c r="D54">
+        <v>12.45011789042404</v>
+      </c>
+      <c r="E54">
+        <v>11.8192</v>
+      </c>
+      <c r="F54">
+        <v>14.2792</v>
+      </c>
+      <c r="G54">
+        <v>2.72</v>
+      </c>
+      <c r="H54">
+        <v>25</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2.8</v>
+      </c>
+      <c r="K54">
+        <v>1.57</v>
+      </c>
+      <c r="L54">
+        <v>1.23</v>
+      </c>
+      <c r="M54">
+        <v>3.40987296</v>
+      </c>
+      <c r="N54">
+        <v>-2.179872960000001</v>
+      </c>
+      <c r="O54">
+        <v>-0.5449682400000002</v>
+      </c>
+      <c r="P54">
+        <v>-1.634904720000001</v>
+      </c>
+      <c r="Q54">
+        <v>-0.06490472000000058</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2242457175371332</v>
+      </c>
+      <c r="T54">
+        <v>2.668737974369629</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.09017931272137479</v>
+      </c>
+      <c r="W54">
+        <v>0.2172651801221357</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3607172508854991</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2226158380813345</v>
+      </c>
+      <c r="C55">
+        <v>0.4808549398929163</v>
+      </c>
+      <c r="D55">
+        <v>12.31465493989292</v>
+      </c>
+      <c r="E55">
+        <v>12.0938</v>
+      </c>
+      <c r="F55">
+        <v>14.5538</v>
+      </c>
+      <c r="G55">
+        <v>2.72</v>
+      </c>
+      <c r="H55">
+        <v>25</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2.8</v>
+      </c>
+      <c r="K55">
+        <v>1.57</v>
+      </c>
+      <c r="L55">
+        <v>1.23</v>
+      </c>
+      <c r="M55">
+        <v>3.47544744</v>
+      </c>
+      <c r="N55">
+        <v>-2.24544744</v>
+      </c>
+      <c r="O55">
+        <v>-0.5613618600000001</v>
+      </c>
+      <c r="P55">
+        <v>-1.68408558</v>
+      </c>
+      <c r="Q55">
+        <v>-0.1140855800000002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.228191371101753</v>
+      </c>
+      <c r="T55">
+        <v>2.72551963339877</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.08847781625493376</v>
+      </c>
+      <c r="W55">
+        <v>0.2176714974783218</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3539112650197351</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2246158380813345</v>
+      </c>
+      <c r="C56">
+        <v>0.07370805834557714</v>
+      </c>
+      <c r="D56">
+        <v>12.18210805834558</v>
+      </c>
+      <c r="E56">
+        <v>12.3684</v>
+      </c>
+      <c r="F56">
+        <v>14.8284</v>
+      </c>
+      <c r="G56">
+        <v>2.72</v>
+      </c>
+      <c r="H56">
+        <v>25</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>2.8</v>
+      </c>
+      <c r="K56">
+        <v>1.57</v>
+      </c>
+      <c r="L56">
+        <v>1.23</v>
+      </c>
+      <c r="M56">
+        <v>3.541021920000001</v>
+      </c>
+      <c r="N56">
+        <v>-2.311021920000001</v>
+      </c>
+      <c r="O56">
+        <v>-0.5777554800000002</v>
+      </c>
+      <c r="P56">
+        <v>-1.733266440000001</v>
+      </c>
+      <c r="Q56">
+        <v>-0.1632664400000006</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2323085748213564</v>
+      </c>
+      <c r="T56">
+        <v>2.784770060211787</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.08683933817613868</v>
+      </c>
+      <c r="W56">
+        <v>0.2180627660435381</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3473573527045548</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2266158380813345</v>
+      </c>
+      <c r="C57">
+        <v>-0.3306159115048271</v>
+      </c>
+      <c r="D57">
+        <v>12.05238408849517</v>
+      </c>
+      <c r="E57">
+        <v>12.643</v>
+      </c>
+      <c r="F57">
+        <v>15.103</v>
+      </c>
+      <c r="G57">
+        <v>2.72</v>
+      </c>
+      <c r="H57">
+        <v>25</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>2.8</v>
+      </c>
+      <c r="K57">
+        <v>1.57</v>
+      </c>
+      <c r="L57">
+        <v>1.23</v>
+      </c>
+      <c r="M57">
+        <v>3.6065964</v>
+      </c>
+      <c r="N57">
+        <v>-2.3765964</v>
+      </c>
+      <c r="O57">
+        <v>-0.5941491000000001</v>
+      </c>
+      <c r="P57">
+        <v>-1.7824473</v>
+      </c>
+      <c r="Q57">
+        <v>-0.2124473000000002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2366087653729421</v>
+      </c>
+      <c r="T57">
+        <v>2.846653839327604</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.08526044111839071</v>
+      </c>
+      <c r="W57">
+        <v>0.2184398066609283</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3410417644735629</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2286158380813345</v>
+      </c>
+      <c r="C58">
+        <v>-0.7322062007274877</v>
+      </c>
+      <c r="D58">
+        <v>11.92539379927251</v>
+      </c>
+      <c r="E58">
+        <v>12.9176</v>
+      </c>
+      <c r="F58">
+        <v>15.3776</v>
+      </c>
+      <c r="G58">
+        <v>2.72</v>
+      </c>
+      <c r="H58">
+        <v>25</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2.8</v>
+      </c>
+      <c r="K58">
+        <v>1.57</v>
+      </c>
+      <c r="L58">
+        <v>1.23</v>
+      </c>
+      <c r="M58">
+        <v>3.672170880000001</v>
+      </c>
+      <c r="N58">
+        <v>-2.442170880000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.6105427200000002</v>
+      </c>
+      <c r="P58">
+        <v>-1.831628160000001</v>
+      </c>
+      <c r="Q58">
+        <v>-0.2616281600000006</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.241104419131418</v>
+      </c>
+      <c r="T58">
+        <v>2.911350517494141</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.08373793324127658</v>
+      </c>
+      <c r="W58">
+        <v>0.2188033815419832</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3349517329651064</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2306158380813345</v>
+      </c>
+      <c r="C59">
+        <v>-1.131148318860776</v>
+      </c>
+      <c r="D59">
+        <v>11.80105168113923</v>
+      </c>
+      <c r="E59">
+        <v>13.1922</v>
+      </c>
+      <c r="F59">
+        <v>15.6522</v>
+      </c>
+      <c r="G59">
+        <v>2.72</v>
+      </c>
+      <c r="H59">
+        <v>25</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2.8</v>
+      </c>
+      <c r="K59">
+        <v>1.57</v>
+      </c>
+      <c r="L59">
+        <v>1.23</v>
+      </c>
+      <c r="M59">
+        <v>3.737745360000001</v>
+      </c>
+      <c r="N59">
+        <v>-2.507745360000001</v>
+      </c>
+      <c r="O59">
+        <v>-0.6269363400000003</v>
+      </c>
+      <c r="P59">
+        <v>-1.880809020000001</v>
+      </c>
+      <c r="Q59">
+        <v>-0.3108090200000009</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2458091730647068</v>
+      </c>
+      <c r="T59">
+        <v>2.979056343482377</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.082268846693184</v>
+      </c>
+      <c r="W59">
+        <v>0.2191541994096677</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.329075386772736</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2326158380813345</v>
+      </c>
+      <c r="C60">
+        <v>-1.527524245926001</v>
+      </c>
+      <c r="D60">
+        <v>11.679275754074</v>
+      </c>
+      <c r="E60">
+        <v>13.4668</v>
+      </c>
+      <c r="F60">
+        <v>15.9268</v>
+      </c>
+      <c r="G60">
+        <v>2.72</v>
+      </c>
+      <c r="H60">
+        <v>25</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2.8</v>
+      </c>
+      <c r="K60">
+        <v>1.57</v>
+      </c>
+      <c r="L60">
+        <v>1.23</v>
+      </c>
+      <c r="M60">
+        <v>3.80331984</v>
+      </c>
+      <c r="N60">
+        <v>-2.573319840000001</v>
+      </c>
+      <c r="O60">
+        <v>-0.6433299600000002</v>
+      </c>
+      <c r="P60">
+        <v>-1.929989880000001</v>
+      </c>
+      <c r="Q60">
+        <v>-0.3599898800000005</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2507379628995807</v>
+      </c>
+      <c r="T60">
+        <v>3.049986256422433</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.08085041830192223</v>
+      </c>
+      <c r="W60">
+        <v>0.219492920109501</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3234016732076889</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2346158380813345</v>
+      </c>
+      <c r="C61">
+        <v>-1.921412612674176</v>
+      </c>
+      <c r="D61">
+        <v>11.55998738732582</v>
+      </c>
+      <c r="E61">
+        <v>13.7414</v>
+      </c>
+      <c r="F61">
+        <v>16.2014</v>
+      </c>
+      <c r="G61">
+        <v>2.72</v>
+      </c>
+      <c r="H61">
+        <v>25</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>2.8</v>
+      </c>
+      <c r="K61">
+        <v>1.57</v>
+      </c>
+      <c r="L61">
+        <v>1.23</v>
+      </c>
+      <c r="M61">
+        <v>3.86889432</v>
+      </c>
+      <c r="N61">
+        <v>-2.63889432</v>
+      </c>
+      <c r="O61">
+        <v>-0.6597235800000001</v>
+      </c>
+      <c r="P61">
+        <v>-1.97917074</v>
+      </c>
+      <c r="Q61">
+        <v>-0.4091707400000002</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2559071815068876</v>
+      </c>
+      <c r="T61">
+        <v>3.124376165115662</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.0794800722290083</v>
+      </c>
+      <c r="W61">
+        <v>0.2198201587517128</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3179202889160332</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2366158380813345</v>
+      </c>
+      <c r="C62">
+        <v>-2.312888869898561</v>
+      </c>
+      <c r="D62">
+        <v>11.44311113010144</v>
+      </c>
+      <c r="E62">
+        <v>14.016</v>
+      </c>
+      <c r="F62">
+        <v>16.476</v>
+      </c>
+      <c r="G62">
+        <v>2.72</v>
+      </c>
+      <c r="H62">
+        <v>25</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2.8</v>
+      </c>
+      <c r="K62">
+        <v>1.57</v>
+      </c>
+      <c r="L62">
+        <v>1.23</v>
+      </c>
+      <c r="M62">
+        <v>3.9344688</v>
+      </c>
+      <c r="N62">
+        <v>-2.7044688</v>
+      </c>
+      <c r="O62">
+        <v>-0.6761172</v>
+      </c>
+      <c r="P62">
+        <v>-2.0283516</v>
+      </c>
+      <c r="Q62">
+        <v>-0.4583515999999996</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2613348610445598</v>
+      </c>
+      <c r="T62">
+        <v>3.202485569243555</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.07815540435852483</v>
+      </c>
+      <c r="W62">
+        <v>0.2201364894391843</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3126216174340993</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2386158380813345</v>
+      </c>
+      <c r="C63">
+        <v>-2.702025447579091</v>
+      </c>
+      <c r="D63">
+        <v>11.32857455242091</v>
+      </c>
+      <c r="E63">
+        <v>14.2906</v>
+      </c>
+      <c r="F63">
+        <v>16.7506</v>
+      </c>
+      <c r="G63">
+        <v>2.72</v>
+      </c>
+      <c r="H63">
+        <v>25</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2.8</v>
+      </c>
+      <c r="K63">
+        <v>1.57</v>
+      </c>
+      <c r="L63">
+        <v>1.23</v>
+      </c>
+      <c r="M63">
+        <v>4.00004328</v>
+      </c>
+      <c r="N63">
+        <v>-2.77004328</v>
+      </c>
+      <c r="O63">
+        <v>-0.6925108200000001</v>
+      </c>
+      <c r="P63">
+        <v>-2.07753246</v>
+      </c>
+      <c r="Q63">
+        <v>-0.5075324600000004</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2670408831226254</v>
+      </c>
+      <c r="T63">
+        <v>3.284600583839543</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.07687416822149983</v>
+      </c>
+      <c r="W63">
+        <v>0.2204424486287059</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3074966728859992</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2406158380813345</v>
+      </c>
+      <c r="C64">
+        <v>-3.088891904564056</v>
+      </c>
+      <c r="D64">
+        <v>11.21630809543595</v>
+      </c>
+      <c r="E64">
+        <v>14.5652</v>
+      </c>
+      <c r="F64">
+        <v>17.0252</v>
+      </c>
+      <c r="G64">
+        <v>2.72</v>
+      </c>
+      <c r="H64">
+        <v>25</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2.8</v>
+      </c>
+      <c r="K64">
+        <v>1.57</v>
+      </c>
+      <c r="L64">
+        <v>1.23</v>
+      </c>
+      <c r="M64">
+        <v>4.06561776</v>
+      </c>
+      <c r="N64">
+        <v>-2.835617760000001</v>
+      </c>
+      <c r="O64">
+        <v>-0.7089044400000002</v>
+      </c>
+      <c r="P64">
+        <v>-2.12671332</v>
+      </c>
+      <c r="Q64">
+        <v>-0.5567133200000003</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2730472221521683</v>
+      </c>
+      <c r="T64">
+        <v>3.371037441309005</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.07563426228244337</v>
+      </c>
+      <c r="W64">
+        <v>0.2207385381669525</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3025370491297734</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2426158380813345</v>
+      </c>
+      <c r="C65">
+        <v>-3.473555069439003</v>
+      </c>
+      <c r="D65">
+        <v>11.106244930561</v>
+      </c>
+      <c r="E65">
+        <v>14.8398</v>
+      </c>
+      <c r="F65">
+        <v>17.2998</v>
+      </c>
+      <c r="G65">
+        <v>2.72</v>
+      </c>
+      <c r="H65">
+        <v>25</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2.8</v>
+      </c>
+      <c r="K65">
+        <v>1.57</v>
+      </c>
+      <c r="L65">
+        <v>1.23</v>
+      </c>
+      <c r="M65">
+        <v>4.131192240000001</v>
+      </c>
+      <c r="N65">
+        <v>-2.901192240000001</v>
+      </c>
+      <c r="O65">
+        <v>-0.7252980600000003</v>
+      </c>
+      <c r="P65">
+        <v>-2.175894180000001</v>
+      </c>
+      <c r="Q65">
+        <v>-0.6058941800000011</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2793782281562809</v>
+      </c>
+      <c r="T65">
+        <v>3.462146561344383</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.07443371843669029</v>
+      </c>
+      <c r="W65">
+        <v>0.2210252280373184</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2977348737467611</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2446158380813345</v>
+      </c>
+      <c r="C66">
+        <v>-3.85607917318239</v>
+      </c>
+      <c r="D66">
+        <v>10.99832082681761</v>
+      </c>
+      <c r="E66">
+        <v>15.1144</v>
+      </c>
+      <c r="F66">
+        <v>17.5744</v>
+      </c>
+      <c r="G66">
+        <v>2.72</v>
+      </c>
+      <c r="H66">
+        <v>25</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2.8</v>
+      </c>
+      <c r="K66">
+        <v>1.57</v>
+      </c>
+      <c r="L66">
+        <v>1.23</v>
+      </c>
+      <c r="M66">
+        <v>4.19676672</v>
+      </c>
+      <c r="N66">
+        <v>-2.966766720000001</v>
+      </c>
+      <c r="O66">
+        <v>-0.7416916800000002</v>
+      </c>
+      <c r="P66">
+        <v>-2.225075040000001</v>
+      </c>
+      <c r="Q66">
+        <v>-0.6550750400000005</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2860609567161776</v>
+      </c>
+      <c r="T66">
+        <v>3.558317299159505</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.07327069158611701</v>
+      </c>
+      <c r="W66">
+        <v>0.2213029588492353</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2930827663444681</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2466158380813345</v>
+      </c>
+      <c r="C67">
+        <v>-4.236525974161177</v>
+      </c>
+      <c r="D67">
+        <v>10.89247402583882</v>
+      </c>
+      <c r="E67">
+        <v>15.389</v>
+      </c>
+      <c r="F67">
+        <v>17.849</v>
+      </c>
+      <c r="G67">
+        <v>2.72</v>
+      </c>
+      <c r="H67">
+        <v>25</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2.8</v>
+      </c>
+      <c r="K67">
+        <v>1.57</v>
+      </c>
+      <c r="L67">
+        <v>1.23</v>
+      </c>
+      <c r="M67">
+        <v>4.2623412</v>
+      </c>
+      <c r="N67">
+        <v>-3.0323412</v>
+      </c>
+      <c r="O67">
+        <v>-0.7580853000000001</v>
+      </c>
+      <c r="P67">
+        <v>-2.2742559</v>
+      </c>
+      <c r="Q67">
+        <v>-0.7042558999999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2931255554794969</v>
+      </c>
+      <c r="T67">
+        <v>3.65998350770692</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.07214345017709985</v>
+      </c>
+      <c r="W67">
+        <v>0.2215721440977086</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2885738007083993</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2486158380813345</v>
+      </c>
+      <c r="C68">
+        <v>-4.614954875977602</v>
+      </c>
+      <c r="D68">
+        <v>10.7886451240224</v>
+      </c>
+      <c r="E68">
+        <v>15.6636</v>
+      </c>
+      <c r="F68">
+        <v>18.1236</v>
+      </c>
+      <c r="G68">
+        <v>2.72</v>
+      </c>
+      <c r="H68">
+        <v>25</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2.8</v>
+      </c>
+      <c r="K68">
+        <v>1.57</v>
+      </c>
+      <c r="L68">
+        <v>1.23</v>
+      </c>
+      <c r="M68">
+        <v>4.32791568</v>
+      </c>
+      <c r="N68">
+        <v>-3.097915680000001</v>
+      </c>
+      <c r="O68">
+        <v>-0.7744789200000002</v>
+      </c>
+      <c r="P68">
+        <v>-2.323436760000001</v>
+      </c>
+      <c r="Q68">
+        <v>-0.7534367600000007</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3006057188759528</v>
+      </c>
+      <c r="T68">
+        <v>3.767630081463006</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.07105036759865893</v>
+      </c>
+      <c r="W68">
+        <v>0.2218331722174403</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2842014703946356</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2506158380813345</v>
+      </c>
+      <c r="C69">
+        <v>-4.99142303863955</v>
+      </c>
+      <c r="D69">
+        <v>10.68677696136045</v>
+      </c>
+      <c r="E69">
+        <v>15.9382</v>
+      </c>
+      <c r="F69">
+        <v>18.3982</v>
+      </c>
+      <c r="G69">
+        <v>2.72</v>
+      </c>
+      <c r="H69">
+        <v>25</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2.8</v>
+      </c>
+      <c r="K69">
+        <v>1.57</v>
+      </c>
+      <c r="L69">
+        <v>1.23</v>
+      </c>
+      <c r="M69">
+        <v>4.393490160000001</v>
+      </c>
+      <c r="N69">
+        <v>-3.163490160000001</v>
+      </c>
+      <c r="O69">
+        <v>-0.7908725400000003</v>
+      </c>
+      <c r="P69">
+        <v>-2.372617620000001</v>
+      </c>
+      <c r="Q69">
+        <v>-0.8026176200000006</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3085392255085574</v>
+      </c>
+      <c r="T69">
+        <v>3.881800689992188</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.06998991435091774</v>
+      </c>
+      <c r="W69">
+        <v>0.2220864084530009</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2799596574036709</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2526158380813345</v>
+      </c>
+      <c r="C70">
+        <v>-5.365985483491693</v>
+      </c>
+      <c r="D70">
+        <v>10.58681451650831</v>
+      </c>
+      <c r="E70">
+        <v>16.2128</v>
+      </c>
+      <c r="F70">
+        <v>18.6728</v>
+      </c>
+      <c r="G70">
+        <v>2.72</v>
+      </c>
+      <c r="H70">
+        <v>25</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2.8</v>
+      </c>
+      <c r="K70">
+        <v>1.57</v>
+      </c>
+      <c r="L70">
+        <v>1.23</v>
+      </c>
+      <c r="M70">
+        <v>4.459064640000001</v>
+      </c>
+      <c r="N70">
+        <v>-3.229064640000002</v>
+      </c>
+      <c r="O70">
+        <v>-0.8072661600000004</v>
+      </c>
+      <c r="P70">
+        <v>-2.421798480000001</v>
+      </c>
+      <c r="Q70">
+        <v>-0.8517984800000014</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3169685763056998</v>
+      </c>
+      <c r="T70">
+        <v>4.003106961554444</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.06896065090458071</v>
+      </c>
+      <c r="W70">
+        <v>0.2223321965639861</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2758426036183228</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2546158380813345</v>
+      </c>
+      <c r="C71">
+        <v>-5.738695192312212</v>
+      </c>
+      <c r="D71">
+        <v>10.48870480768779</v>
+      </c>
+      <c r="E71">
+        <v>16.4874</v>
+      </c>
+      <c r="F71">
+        <v>18.9474</v>
+      </c>
+      <c r="G71">
+        <v>2.72</v>
+      </c>
+      <c r="H71">
+        <v>25</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2.8</v>
+      </c>
+      <c r="K71">
+        <v>1.57</v>
+      </c>
+      <c r="L71">
+        <v>1.23</v>
+      </c>
+      <c r="M71">
+        <v>4.524639120000001</v>
+      </c>
+      <c r="N71">
+        <v>-3.294639120000001</v>
+      </c>
+      <c r="O71">
+        <v>-0.8236597800000003</v>
+      </c>
+      <c r="P71">
+        <v>-2.470979340000001</v>
+      </c>
+      <c r="Q71">
+        <v>-0.9009793400000008</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3259417561865288</v>
+      </c>
+      <c r="T71">
+        <v>4.132239444185232</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.06796122118132593</v>
+      </c>
+      <c r="W71">
+        <v>0.2225708603818994</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2718448847253037</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2566158380813345</v>
+      </c>
+      <c r="C72">
+        <v>-6.109603200949962</v>
+      </c>
+      <c r="D72">
+        <v>10.39239679905004</v>
+      </c>
+      <c r="E72">
+        <v>16.762</v>
+      </c>
+      <c r="F72">
+        <v>19.222</v>
+      </c>
+      <c r="G72">
+        <v>2.72</v>
+      </c>
+      <c r="H72">
+        <v>25</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2.8</v>
+      </c>
+      <c r="K72">
+        <v>1.57</v>
+      </c>
+      <c r="L72">
+        <v>1.23</v>
+      </c>
+      <c r="M72">
+        <v>4.5902136</v>
+      </c>
+      <c r="N72">
+        <v>-3.360213600000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.8400534000000002</v>
+      </c>
+      <c r="P72">
+        <v>-2.5201602</v>
+      </c>
+      <c r="Q72">
+        <v>-0.9501602000000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3355131480594131</v>
+      </c>
+      <c r="T72">
+        <v>4.269980758991407</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.06699034659302128</v>
+      </c>
+      <c r="W72">
+        <v>0.2228027052335865</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2679613863720851</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2586158380813345</v>
+      </c>
+      <c r="C73">
+        <v>-6.478758687849906</v>
+      </c>
+      <c r="D73">
+        <v>10.29784131215009</v>
+      </c>
+      <c r="E73">
+        <v>17.0366</v>
+      </c>
+      <c r="F73">
+        <v>19.4966</v>
+      </c>
+      <c r="G73">
+        <v>2.72</v>
+      </c>
+      <c r="H73">
+        <v>25</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2.8</v>
+      </c>
+      <c r="K73">
+        <v>1.57</v>
+      </c>
+      <c r="L73">
+        <v>1.23</v>
+      </c>
+      <c r="M73">
+        <v>4.655788080000001</v>
+      </c>
+      <c r="N73">
+        <v>-3.425788080000001</v>
+      </c>
+      <c r="O73">
+        <v>-0.8564470200000003</v>
+      </c>
+      <c r="P73">
+        <v>-2.569341060000001</v>
+      </c>
+      <c r="Q73">
+        <v>-0.999341060000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3457446359235308</v>
+      </c>
+      <c r="T73">
+        <v>4.417221474818696</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.06604682058466886</v>
+      </c>
+      <c r="W73">
+        <v>0.2230280192443811</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2641872823386754</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2606158380813345</v>
+      </c>
+      <c r="C74">
+        <v>-6.846209057789443</v>
+      </c>
+      <c r="D74">
+        <v>10.20499094221056</v>
+      </c>
+      <c r="E74">
+        <v>17.3112</v>
+      </c>
+      <c r="F74">
+        <v>19.7712</v>
+      </c>
+      <c r="G74">
+        <v>2.72</v>
+      </c>
+      <c r="H74">
+        <v>25</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2.8</v>
+      </c>
+      <c r="K74">
+        <v>1.57</v>
+      </c>
+      <c r="L74">
+        <v>1.23</v>
+      </c>
+      <c r="M74">
+        <v>4.72136256</v>
+      </c>
+      <c r="N74">
+        <v>-3.491362560000001</v>
+      </c>
+      <c r="O74">
+        <v>-0.8728406400000002</v>
+      </c>
+      <c r="P74">
+        <v>-2.618521920000001</v>
+      </c>
+      <c r="Q74">
+        <v>-1.04852192</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3567069443493711</v>
+      </c>
+      <c r="T74">
+        <v>4.574979384633648</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.06512950363210401</v>
+      </c>
+      <c r="W74">
+        <v>0.2232470745326536</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2605180145284161</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2626158380813345</v>
+      </c>
+      <c r="C75">
+        <v>-7.21200002112513</v>
+      </c>
+      <c r="D75">
+        <v>10.11379997887487</v>
+      </c>
+      <c r="E75">
+        <v>17.5858</v>
+      </c>
+      <c r="F75">
+        <v>20.0458</v>
+      </c>
+      <c r="G75">
+        <v>2.72</v>
+      </c>
+      <c r="H75">
+        <v>25</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2.8</v>
+      </c>
+      <c r="K75">
+        <v>1.57</v>
+      </c>
+      <c r="L75">
+        <v>1.23</v>
+      </c>
+      <c r="M75">
+        <v>4.786937040000001</v>
+      </c>
+      <c r="N75">
+        <v>-3.556937040000001</v>
+      </c>
+      <c r="O75">
+        <v>-0.8892342600000003</v>
+      </c>
+      <c r="P75">
+        <v>-2.667702780000001</v>
+      </c>
+      <c r="Q75">
+        <v>-1.097702780000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3684812756215701</v>
+      </c>
+      <c r="T75">
+        <v>4.744423065546006</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.06423731865084231</v>
+      </c>
+      <c r="W75">
+        <v>0.2234601283061789</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2569492746033692</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2646158380813345</v>
+      </c>
+      <c r="C76">
+        <v>-7.576175668828212</v>
+      </c>
+      <c r="D76">
+        <v>10.02422433117179</v>
+      </c>
+      <c r="E76">
+        <v>17.8604</v>
+      </c>
+      <c r="F76">
+        <v>20.3204</v>
+      </c>
+      <c r="G76">
+        <v>2.72</v>
+      </c>
+      <c r="H76">
+        <v>25</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2.8</v>
+      </c>
+      <c r="K76">
+        <v>1.57</v>
+      </c>
+      <c r="L76">
+        <v>1.23</v>
+      </c>
+      <c r="M76">
+        <v>4.85251152</v>
+      </c>
+      <c r="N76">
+        <v>-3.622511520000001</v>
+      </c>
+      <c r="O76">
+        <v>-0.9056278800000002</v>
+      </c>
+      <c r="P76">
+        <v>-2.716883640000001</v>
+      </c>
+      <c r="Q76">
+        <v>-1.146883640000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3811613246839381</v>
+      </c>
+      <c r="T76">
+        <v>4.926900875759314</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.06336924677718229</v>
+      </c>
+      <c r="W76">
+        <v>0.2236674238696089</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2534769871087291</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2666158380813345</v>
+      </c>
+      <c r="C77">
+        <v>-7.9387785435677</v>
+      </c>
+      <c r="D77">
+        <v>9.936221456432298</v>
+      </c>
+      <c r="E77">
+        <v>18.135</v>
+      </c>
+      <c r="F77">
+        <v>20.595</v>
+      </c>
+      <c r="G77">
+        <v>2.72</v>
+      </c>
+      <c r="H77">
+        <v>25</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2.8</v>
+      </c>
+      <c r="K77">
+        <v>1.57</v>
+      </c>
+      <c r="L77">
+        <v>1.23</v>
+      </c>
+      <c r="M77">
+        <v>4.918086</v>
+      </c>
+      <c r="N77">
+        <v>-3.688086</v>
+      </c>
+      <c r="O77">
+        <v>-0.9220215</v>
+      </c>
+      <c r="P77">
+        <v>-2.7660645</v>
+      </c>
+      <c r="Q77">
+        <v>-1.1960645</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3948557776712957</v>
+      </c>
+      <c r="T77">
+        <v>5.123976910789687</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.06252432348681987</v>
+      </c>
+      <c r="W77">
+        <v>0.2238691915513474</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2500972939472794</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2686158380813345</v>
+      </c>
+      <c r="C78">
+        <v>-8.299849707081819</v>
+      </c>
+      <c r="D78">
+        <v>9.849750292918182</v>
+      </c>
+      <c r="E78">
+        <v>18.4096</v>
+      </c>
+      <c r="F78">
+        <v>20.8696</v>
+      </c>
+      <c r="G78">
+        <v>2.72</v>
+      </c>
+      <c r="H78">
+        <v>25</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2.8</v>
+      </c>
+      <c r="K78">
+        <v>1.57</v>
+      </c>
+      <c r="L78">
+        <v>1.23</v>
+      </c>
+      <c r="M78">
+        <v>4.983660480000001</v>
+      </c>
+      <c r="N78">
+        <v>-3.753660480000002</v>
+      </c>
+      <c r="O78">
+        <v>-0.9384151200000004</v>
+      </c>
+      <c r="P78">
+        <v>-2.815245360000001</v>
+      </c>
+      <c r="Q78">
+        <v>-1.245245360000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4096914350742664</v>
+      </c>
+      <c r="T78">
+        <v>5.337475948739257</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.06170163501988801</v>
+      </c>
+      <c r="W78">
+        <v>0.2240656495572508</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2468065400795519</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2706158380813345</v>
+      </c>
+      <c r="C79">
+        <v>-8.659428804061916</v>
+      </c>
+      <c r="D79">
+        <v>9.764771195938085</v>
+      </c>
+      <c r="E79">
+        <v>18.6842</v>
+      </c>
+      <c r="F79">
+        <v>21.1442</v>
+      </c>
+      <c r="G79">
+        <v>2.72</v>
+      </c>
+      <c r="H79">
+        <v>25</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2.8</v>
+      </c>
+      <c r="K79">
+        <v>1.57</v>
+      </c>
+      <c r="L79">
+        <v>1.23</v>
+      </c>
+      <c r="M79">
+        <v>5.049234960000001</v>
+      </c>
+      <c r="N79">
+        <v>-3.819234960000001</v>
+      </c>
+      <c r="O79">
+        <v>-0.9548087400000003</v>
+      </c>
+      <c r="P79">
+        <v>-2.864426220000001</v>
+      </c>
+      <c r="Q79">
+        <v>-1.294426220000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4258171496427127</v>
+      </c>
+      <c r="T79">
+        <v>5.569540120423573</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.06090031508456479</v>
+      </c>
+      <c r="W79">
+        <v>0.2242570047578059</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2436012603382591</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2726158380813345</v>
+      </c>
+      <c r="C80">
+        <v>-9.017554122757746</v>
+      </c>
+      <c r="D80">
+        <v>9.681245877242254</v>
+      </c>
+      <c r="E80">
+        <v>18.9588</v>
+      </c>
+      <c r="F80">
+        <v>21.4188</v>
+      </c>
+      <c r="G80">
+        <v>2.72</v>
+      </c>
+      <c r="H80">
+        <v>25</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2.8</v>
+      </c>
+      <c r="K80">
+        <v>1.57</v>
+      </c>
+      <c r="L80">
+        <v>1.23</v>
+      </c>
+      <c r="M80">
+        <v>5.11480944</v>
+      </c>
+      <c r="N80">
+        <v>-3.884809440000001</v>
+      </c>
+      <c r="O80">
+        <v>-0.9712023600000002</v>
+      </c>
+      <c r="P80">
+        <v>-2.91360708</v>
+      </c>
+      <c r="Q80">
+        <v>-1.34360708</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4434088382628361</v>
+      </c>
+      <c r="T80">
+        <v>5.822701034988281</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.06011954181424986</v>
+      </c>
+      <c r="W80">
+        <v>0.2244434534147572</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2404781672569994</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2746158380813345</v>
+      </c>
+      <c r="C81">
+        <v>-9.374262652498679</v>
+      </c>
+      <c r="D81">
+        <v>9.599137347501321</v>
+      </c>
+      <c r="E81">
+        <v>19.2334</v>
+      </c>
+      <c r="F81">
+        <v>21.6934</v>
+      </c>
+      <c r="G81">
+        <v>2.72</v>
+      </c>
+      <c r="H81">
+        <v>25</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2.8</v>
+      </c>
+      <c r="K81">
+        <v>1.57</v>
+      </c>
+      <c r="L81">
+        <v>1.23</v>
+      </c>
+      <c r="M81">
+        <v>5.180383920000001</v>
+      </c>
+      <c r="N81">
+        <v>-3.950383920000001</v>
+      </c>
+      <c r="O81">
+        <v>-0.9875959800000003</v>
+      </c>
+      <c r="P81">
+        <v>-2.962787940000001</v>
+      </c>
+      <c r="Q81">
+        <v>-1.392787940000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4626759257991615</v>
+      </c>
+      <c r="T81">
+        <v>6.099972512844865</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.05935853495584163</v>
+      </c>
+      <c r="W81">
+        <v>0.224625181852545</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2374341398233665</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2766158380813345</v>
+      </c>
+      <c r="C82">
+        <v>-9.729590138312462</v>
+      </c>
+      <c r="D82">
+        <v>9.518409861687541</v>
+      </c>
+      <c r="E82">
+        <v>19.508</v>
+      </c>
+      <c r="F82">
+        <v>21.968</v>
+      </c>
+      <c r="G82">
+        <v>2.72</v>
+      </c>
+      <c r="H82">
+        <v>25</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2.8</v>
+      </c>
+      <c r="K82">
+        <v>1.57</v>
+      </c>
+      <c r="L82">
+        <v>1.23</v>
+      </c>
+      <c r="M82">
+        <v>5.245958400000001</v>
+      </c>
+      <c r="N82">
+        <v>-4.015958400000001</v>
+      </c>
+      <c r="O82">
+        <v>-1.0039896</v>
+      </c>
+      <c r="P82">
+        <v>-3.011968800000001</v>
+      </c>
+      <c r="Q82">
+        <v>-1.441968800000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4838697220891197</v>
+      </c>
+      <c r="T82">
+        <v>6.40497113848711</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.05861655326889361</v>
+      </c>
+      <c r="W82">
+        <v>0.2248023670793882</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2344662130755744</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2786158380813345</v>
+      </c>
+      <c r="C83">
+        <v>-10.08357113281091</v>
+      </c>
+      <c r="D83">
+        <v>9.439028867189094</v>
+      </c>
+      <c r="E83">
+        <v>19.7826</v>
+      </c>
+      <c r="F83">
+        <v>22.2426</v>
+      </c>
+      <c r="G83">
+        <v>2.72</v>
+      </c>
+      <c r="H83">
+        <v>25</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2.8</v>
+      </c>
+      <c r="K83">
+        <v>1.57</v>
+      </c>
+      <c r="L83">
+        <v>1.23</v>
+      </c>
+      <c r="M83">
+        <v>5.311532880000001</v>
+      </c>
+      <c r="N83">
+        <v>-4.081532880000001</v>
+      </c>
+      <c r="O83">
+        <v>-1.02038322</v>
+      </c>
+      <c r="P83">
+        <v>-3.061149660000001</v>
+      </c>
+      <c r="Q83">
+        <v>-1.491149660000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5072944443043366</v>
+      </c>
+      <c r="T83">
+        <v>6.742074882618011</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.05789289211742579</v>
+      </c>
+      <c r="W83">
+        <v>0.2249751773623588</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2315715684697032</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2806158380813345</v>
+      </c>
+      <c r="C84">
+        <v>-10.43623904550085</v>
+      </c>
+      <c r="D84">
+        <v>9.360960954499156</v>
+      </c>
+      <c r="E84">
+        <v>20.0572</v>
+      </c>
+      <c r="F84">
+        <v>22.5172</v>
+      </c>
+      <c r="G84">
+        <v>2.72</v>
+      </c>
+      <c r="H84">
+        <v>25</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2.8</v>
+      </c>
+      <c r="K84">
+        <v>1.57</v>
+      </c>
+      <c r="L84">
+        <v>1.23</v>
+      </c>
+      <c r="M84">
+        <v>5.377107360000001</v>
+      </c>
+      <c r="N84">
+        <v>-4.147107360000001</v>
+      </c>
+      <c r="O84">
+        <v>-1.03677684</v>
+      </c>
+      <c r="P84">
+        <v>-3.110330520000001</v>
+      </c>
+      <c r="Q84">
+        <v>-1.540330520000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5333219134323552</v>
+      </c>
+      <c r="T84">
+        <v>7.116634598319012</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.05718688123794499</v>
+      </c>
+      <c r="W84">
+        <v>0.2251437727603788</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2287475249517799</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2826158380813345</v>
+      </c>
+      <c r="C85">
+        <v>-10.78762618966805</v>
+      </c>
+      <c r="D85">
+        <v>9.284173810331954</v>
+      </c>
+      <c r="E85">
+        <v>20.3318</v>
+      </c>
+      <c r="F85">
+        <v>22.7918</v>
+      </c>
+      <c r="G85">
+        <v>2.72</v>
+      </c>
+      <c r="H85">
+        <v>25</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2.8</v>
+      </c>
+      <c r="K85">
+        <v>1.57</v>
+      </c>
+      <c r="L85">
+        <v>1.23</v>
+      </c>
+      <c r="M85">
+        <v>5.442681840000001</v>
+      </c>
+      <c r="N85">
+        <v>-4.212681840000001</v>
+      </c>
+      <c r="O85">
+        <v>-1.05317046</v>
+      </c>
+      <c r="P85">
+        <v>-3.159511380000001</v>
+      </c>
+      <c r="Q85">
+        <v>-1.58951138</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5624114377519056</v>
+      </c>
+      <c r="T85">
+        <v>7.535260162926013</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.05649788266881312</v>
+      </c>
+      <c r="W85">
+        <v>0.2253083056186874</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2259915306752525</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2846158380813345</v>
+      </c>
+      <c r="C86">
+        <v>-11.13776382697244</v>
+      </c>
+      <c r="D86">
+        <v>9.208636173027559</v>
+      </c>
+      <c r="E86">
+        <v>20.6064</v>
+      </c>
+      <c r="F86">
+        <v>23.0664</v>
+      </c>
+      <c r="G86">
+        <v>2.72</v>
+      </c>
+      <c r="H86">
+        <v>25</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2.8</v>
+      </c>
+      <c r="K86">
+        <v>1.57</v>
+      </c>
+      <c r="L86">
+        <v>1.23</v>
+      </c>
+      <c r="M86">
+        <v>5.508256320000001</v>
+      </c>
+      <c r="N86">
+        <v>-4.278256320000001</v>
+      </c>
+      <c r="O86">
+        <v>-1.06956408</v>
+      </c>
+      <c r="P86">
+        <v>-3.208692240000001</v>
+      </c>
+      <c r="Q86">
+        <v>-1.638692240000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5951371526113995</v>
+      </c>
+      <c r="T86">
+        <v>8.006213923108886</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.05582528882751772</v>
+      </c>
+      <c r="W86">
+        <v>0.2254689210279888</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2233011553100709</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2866158380813345</v>
+      </c>
+      <c r="C87">
+        <v>-11.48668220988391</v>
+      </c>
+      <c r="D87">
+        <v>9.134317790116089</v>
+      </c>
+      <c r="E87">
+        <v>20.881</v>
+      </c>
+      <c r="F87">
+        <v>23.341</v>
+      </c>
+      <c r="G87">
+        <v>2.72</v>
+      </c>
+      <c r="H87">
+        <v>25</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2.8</v>
+      </c>
+      <c r="K87">
+        <v>1.57</v>
+      </c>
+      <c r="L87">
+        <v>1.23</v>
+      </c>
+      <c r="M87">
+        <v>5.573830800000001</v>
+      </c>
+      <c r="N87">
+        <v>-4.343830800000001</v>
+      </c>
+      <c r="O87">
+        <v>-1.0859577</v>
+      </c>
+      <c r="P87">
+        <v>-3.257873100000001</v>
+      </c>
+      <c r="Q87">
+        <v>-1.687873100000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6322262961188261</v>
+      </c>
+      <c r="T87">
+        <v>8.53996151798281</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05516852072366458</v>
+      </c>
+      <c r="W87">
+        <v>0.2256257572511889</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2206740828946583</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2886158380813345</v>
+      </c>
+      <c r="C88">
+        <v>-11.83441062207963</v>
+      </c>
+      <c r="D88">
+        <v>9.061189377920366</v>
+      </c>
+      <c r="E88">
+        <v>21.1556</v>
+      </c>
+      <c r="F88">
+        <v>23.6156</v>
+      </c>
+      <c r="G88">
+        <v>2.72</v>
+      </c>
+      <c r="H88">
+        <v>25</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2.8</v>
+      </c>
+      <c r="K88">
+        <v>1.57</v>
+      </c>
+      <c r="L88">
+        <v>1.23</v>
+      </c>
+      <c r="M88">
+        <v>5.63940528</v>
+      </c>
+      <c r="N88">
+        <v>-4.409405280000001</v>
+      </c>
+      <c r="O88">
+        <v>-1.10235132</v>
+      </c>
+      <c r="P88">
+        <v>-3.30705396</v>
+      </c>
+      <c r="Q88">
+        <v>-1.73705396</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6746138886987423</v>
+      </c>
+      <c r="T88">
+        <v>9.149958769267299</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05452702629664523</v>
+      </c>
+      <c r="W88">
+        <v>0.2257789461203611</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2181081051865809</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2906158380813345</v>
+      </c>
+      <c r="C89">
+        <v>-12.18097741691637</v>
+      </c>
+      <c r="D89">
+        <v>8.989222583083629</v>
+      </c>
+      <c r="E89">
+        <v>21.4302</v>
+      </c>
+      <c r="F89">
+        <v>23.8902</v>
+      </c>
+      <c r="G89">
+        <v>2.72</v>
+      </c>
+      <c r="H89">
+        <v>25</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2.8</v>
+      </c>
+      <c r="K89">
+        <v>1.57</v>
+      </c>
+      <c r="L89">
+        <v>1.23</v>
+      </c>
+      <c r="M89">
+        <v>5.704979760000001</v>
+      </c>
+      <c r="N89">
+        <v>-4.474979760000001</v>
+      </c>
+      <c r="O89">
+        <v>-1.11874494</v>
+      </c>
+      <c r="P89">
+        <v>-3.356234820000001</v>
+      </c>
+      <c r="Q89">
+        <v>-1.786234820000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7235226493678761</v>
+      </c>
+      <c r="T89">
+        <v>9.853801751518628</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05390027886794815</v>
+      </c>
+      <c r="W89">
+        <v>0.225928613406334</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2156011154717926</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2926158380813345</v>
+      </c>
+      <c r="C90">
+        <v>-12.52641005408382</v>
+      </c>
+      <c r="D90">
+        <v>8.918389945916177</v>
+      </c>
+      <c r="E90">
+        <v>21.7048</v>
+      </c>
+      <c r="F90">
+        <v>24.1648</v>
+      </c>
+      <c r="G90">
+        <v>2.72</v>
+      </c>
+      <c r="H90">
+        <v>25</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2.8</v>
+      </c>
+      <c r="K90">
+        <v>1.57</v>
+      </c>
+      <c r="L90">
+        <v>1.23</v>
+      </c>
+      <c r="M90">
+        <v>5.77055424</v>
+      </c>
+      <c r="N90">
+        <v>-4.540554240000001</v>
+      </c>
+      <c r="O90">
+        <v>-1.13513856</v>
+      </c>
+      <c r="P90">
+        <v>-3.40541568</v>
+      </c>
+      <c r="Q90">
+        <v>-1.83541568</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7805828701485327</v>
+      </c>
+      <c r="T90">
+        <v>10.67495189747851</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.0532877756989942</v>
+      </c>
+      <c r="W90">
+        <v>0.2260748791630802</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2131511027959767</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2946158380813345</v>
+      </c>
+      <c r="C91">
+        <v>-12.87073513453862</v>
+      </c>
+      <c r="D91">
+        <v>8.848664865461382</v>
+      </c>
+      <c r="E91">
+        <v>21.9794</v>
+      </c>
+      <c r="F91">
+        <v>24.4394</v>
+      </c>
+      <c r="G91">
+        <v>2.72</v>
+      </c>
+      <c r="H91">
+        <v>25</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>2.8</v>
+      </c>
+      <c r="K91">
+        <v>1.57</v>
+      </c>
+      <c r="L91">
+        <v>1.23</v>
+      </c>
+      <c r="M91">
+        <v>5.836128720000001</v>
+      </c>
+      <c r="N91">
+        <v>-4.606128720000002</v>
+      </c>
+      <c r="O91">
+        <v>-1.15153218</v>
+      </c>
+      <c r="P91">
+        <v>-3.454596540000002</v>
+      </c>
+      <c r="Q91">
+        <v>-1.884596540000002</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8480176765256722</v>
+      </c>
+      <c r="T91">
+        <v>11.64540206997656</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.0526890366461965</v>
+      </c>
+      <c r="W91">
+        <v>0.2262178580488883</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2107561465847859</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2966158380813345</v>
+      </c>
+      <c r="C92">
+        <v>-13.21397843381235</v>
+      </c>
+      <c r="D92">
+        <v>8.780021566187656</v>
+      </c>
+      <c r="E92">
+        <v>22.254</v>
+      </c>
+      <c r="F92">
+        <v>24.714</v>
+      </c>
+      <c r="G92">
+        <v>2.72</v>
+      </c>
+      <c r="H92">
+        <v>25</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>2.8</v>
+      </c>
+      <c r="K92">
+        <v>1.57</v>
+      </c>
+      <c r="L92">
+        <v>1.23</v>
+      </c>
+      <c r="M92">
+        <v>5.901703200000001</v>
+      </c>
+      <c r="N92">
+        <v>-4.671703200000001</v>
+      </c>
+      <c r="O92">
+        <v>-1.1679258</v>
+      </c>
+      <c r="P92">
+        <v>-3.503777400000001</v>
+      </c>
+      <c r="Q92">
+        <v>-1.933777400000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.9289394441782395</v>
+      </c>
+      <c r="T92">
+        <v>12.80994227697422</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.05210360290568321</v>
+      </c>
+      <c r="W92">
+        <v>0.2263576596261229</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2084144116227328</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2986158380813345</v>
+      </c>
+      <c r="C93">
+        <v>-13.55616493378113</v>
+      </c>
+      <c r="D93">
+        <v>8.712435066218868</v>
+      </c>
+      <c r="E93">
+        <v>22.5286</v>
+      </c>
+      <c r="F93">
+        <v>24.9886</v>
+      </c>
+      <c r="G93">
+        <v>2.72</v>
+      </c>
+      <c r="H93">
+        <v>25</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2.8</v>
+      </c>
+      <c r="K93">
+        <v>1.57</v>
+      </c>
+      <c r="L93">
+        <v>1.23</v>
+      </c>
+      <c r="M93">
+        <v>5.96727768</v>
+      </c>
+      <c r="N93">
+        <v>-4.737277680000001</v>
+      </c>
+      <c r="O93">
+        <v>-1.18431942</v>
+      </c>
+      <c r="P93">
+        <v>-3.55295826</v>
+      </c>
+      <c r="Q93">
+        <v>-1.98295826</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.027843826864711</v>
+      </c>
+      <c r="T93">
+        <v>14.23326919663802</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.0515310358407856</v>
+      </c>
+      <c r="W93">
+        <v>0.2264943886412204</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2061241433631423</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3006158380813345</v>
+      </c>
+      <c r="C94">
+        <v>-13.89731885297919</v>
+      </c>
+      <c r="D94">
+        <v>8.645881147020807</v>
+      </c>
+      <c r="E94">
+        <v>22.8032</v>
+      </c>
+      <c r="F94">
+        <v>25.2632</v>
+      </c>
+      <c r="G94">
+        <v>2.72</v>
+      </c>
+      <c r="H94">
+        <v>25</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2.8</v>
+      </c>
+      <c r="K94">
+        <v>1.57</v>
+      </c>
+      <c r="L94">
+        <v>1.23</v>
+      </c>
+      <c r="M94">
+        <v>6.032852160000001</v>
+      </c>
+      <c r="N94">
+        <v>-4.802852160000001</v>
+      </c>
+      <c r="O94">
+        <v>-1.20071304</v>
+      </c>
+      <c r="P94">
+        <v>-3.602139120000001</v>
+      </c>
+      <c r="Q94">
+        <v>-2.032139120000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.1514743052228</v>
+      </c>
+      <c r="T94">
+        <v>16.01242784621778</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05097091588599444</v>
+      </c>
+      <c r="W94">
+        <v>0.2266281452864245</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2038836635439777</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3026158380813345</v>
+      </c>
+      <c r="C95">
+        <v>-14.23746367553344</v>
+      </c>
+      <c r="D95">
+        <v>8.580336324466556</v>
+      </c>
+      <c r="E95">
+        <v>23.0778</v>
+      </c>
+      <c r="F95">
+        <v>25.5378</v>
+      </c>
+      <c r="G95">
+        <v>2.72</v>
+      </c>
+      <c r="H95">
+        <v>25</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>2.8</v>
+      </c>
+      <c r="K95">
+        <v>1.57</v>
+      </c>
+      <c r="L95">
+        <v>1.23</v>
+      </c>
+      <c r="M95">
+        <v>6.09842664</v>
+      </c>
+      <c r="N95">
+        <v>-4.868426640000001</v>
+      </c>
+      <c r="O95">
+        <v>-1.21710666</v>
+      </c>
+      <c r="P95">
+        <v>-3.651319980000001</v>
+      </c>
+      <c r="Q95">
+        <v>-2.081319980000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.310427777397485</v>
+      </c>
+      <c r="T95">
+        <v>18.29991753853461</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05042284152162892</v>
+      </c>
+      <c r="W95">
+        <v>0.226759025444635</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2016913660865156</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3046158380813345</v>
+      </c>
+      <c r="C96">
+        <v>-14.57662217879194</v>
+      </c>
+      <c r="D96">
+        <v>8.515777821208061</v>
+      </c>
+      <c r="E96">
+        <v>23.3524</v>
+      </c>
+      <c r="F96">
+        <v>25.8124</v>
+      </c>
+      <c r="G96">
+        <v>2.72</v>
+      </c>
+      <c r="H96">
+        <v>25</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2.8</v>
+      </c>
+      <c r="K96">
+        <v>1.57</v>
+      </c>
+      <c r="L96">
+        <v>1.23</v>
+      </c>
+      <c r="M96">
+        <v>6.164001120000001</v>
+      </c>
+      <c r="N96">
+        <v>-4.934001120000001</v>
+      </c>
+      <c r="O96">
+        <v>-1.23350028</v>
+      </c>
+      <c r="P96">
+        <v>-3.700500840000001</v>
+      </c>
+      <c r="Q96">
+        <v>-2.130500840000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.522365740297067</v>
+      </c>
+      <c r="T96">
+        <v>21.34990379495705</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04988642831395201</v>
+      </c>
+      <c r="W96">
+        <v>0.2268871209186283</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1995457132558081</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3066158380813345</v>
+      </c>
+      <c r="C97">
+        <v>-14.91481645971435</v>
+      </c>
+      <c r="D97">
+        <v>8.452183540285649</v>
+      </c>
+      <c r="E97">
+        <v>23.627</v>
+      </c>
+      <c r="F97">
+        <v>26.087</v>
+      </c>
+      <c r="G97">
+        <v>2.72</v>
+      </c>
+      <c r="H97">
+        <v>25</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>2.8</v>
+      </c>
+      <c r="K97">
+        <v>1.57</v>
+      </c>
+      <c r="L97">
+        <v>1.23</v>
+      </c>
+      <c r="M97">
+        <v>6.229575600000001</v>
+      </c>
+      <c r="N97">
+        <v>-4.999575600000002</v>
+      </c>
+      <c r="O97">
+        <v>-1.2498939</v>
+      </c>
+      <c r="P97">
+        <v>-3.749681700000001</v>
+      </c>
+      <c r="Q97">
+        <v>-2.179681700000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.819078888356481</v>
+      </c>
+      <c r="T97">
+        <v>25.61988455394847</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0493613080159104</v>
+      </c>
+      <c r="W97">
+        <v>0.2270125196458006</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1974452320636416</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3086158380813345</v>
+      </c>
+      <c r="C98">
+        <v>-15.25206796008875</v>
+      </c>
+      <c r="D98">
+        <v>8.38953203991125</v>
+      </c>
+      <c r="E98">
+        <v>23.9016</v>
+      </c>
+      <c r="F98">
+        <v>26.3616</v>
+      </c>
+      <c r="G98">
+        <v>2.72</v>
+      </c>
+      <c r="H98">
+        <v>25</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2.8</v>
+      </c>
+      <c r="K98">
+        <v>1.57</v>
+      </c>
+      <c r="L98">
+        <v>1.23</v>
+      </c>
+      <c r="M98">
+        <v>6.29515008</v>
+      </c>
+      <c r="N98">
+        <v>-5.06515008</v>
+      </c>
+      <c r="O98">
+        <v>-1.26628752</v>
+      </c>
+      <c r="P98">
+        <v>-3.79886256</v>
+      </c>
+      <c r="Q98">
+        <v>-2.22886256</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.264148610445596</v>
+      </c>
+      <c r="T98">
+        <v>32.02485569243552</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04884712772407802</v>
+      </c>
+      <c r="W98">
+        <v>0.2271353058994902</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.195388510896312</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3106158380813345</v>
+      </c>
+      <c r="C99">
+        <v>-15.5883974906351</v>
+      </c>
+      <c r="D99">
+        <v>8.327802509364902</v>
+      </c>
+      <c r="E99">
+        <v>24.1762</v>
+      </c>
+      <c r="F99">
+        <v>26.6362</v>
+      </c>
+      <c r="G99">
+        <v>2.72</v>
+      </c>
+      <c r="H99">
+        <v>25</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>2.8</v>
+      </c>
+      <c r="K99">
+        <v>1.57</v>
+      </c>
+      <c r="L99">
+        <v>1.23</v>
+      </c>
+      <c r="M99">
+        <v>6.36072456</v>
+      </c>
+      <c r="N99">
+        <v>-5.130724560000001</v>
+      </c>
+      <c r="O99">
+        <v>-1.28268114</v>
+      </c>
+      <c r="P99">
+        <v>-3.848043420000001</v>
+      </c>
+      <c r="Q99">
+        <v>-2.27804342</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.005931480594129</v>
+      </c>
+      <c r="T99">
+        <v>42.69980758991403</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04834354908774731</v>
+      </c>
+      <c r="W99">
+        <v>0.227255560477846</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1933741963509892</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3126158380813345</v>
+      </c>
+      <c r="C100">
+        <v>-15.92382525405243</v>
+      </c>
+      <c r="D100">
+        <v>8.266974745947573</v>
+      </c>
+      <c r="E100">
+        <v>24.4508</v>
+      </c>
+      <c r="F100">
+        <v>26.9108</v>
+      </c>
+      <c r="G100">
+        <v>2.72</v>
+      </c>
+      <c r="H100">
+        <v>25</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2.8</v>
+      </c>
+      <c r="K100">
+        <v>1.57</v>
+      </c>
+      <c r="L100">
+        <v>1.23</v>
+      </c>
+      <c r="M100">
+        <v>6.426299040000001</v>
+      </c>
+      <c r="N100">
+        <v>-5.196299040000001</v>
+      </c>
+      <c r="O100">
+        <v>-1.29907476</v>
+      </c>
+      <c r="P100">
+        <v>-3.897224280000001</v>
+      </c>
+      <c r="Q100">
+        <v>-2.327224280000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.489497220891193</v>
+      </c>
+      <c r="T100">
+        <v>64.04971138487103</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.04785024756644377</v>
+      </c>
+      <c r="W100">
+        <v>0.2273733608811332</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1914009902657751</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3146158380813345</v>
+      </c>
+      <c r="C101">
+        <v>-16.25837086706331</v>
+      </c>
+      <c r="D101">
+        <v>8.207029132936693</v>
+      </c>
+      <c r="E101">
+        <v>24.7254</v>
+      </c>
+      <c r="F101">
+        <v>27.1854</v>
+      </c>
+      <c r="G101">
+        <v>2.72</v>
+      </c>
+      <c r="H101">
+        <v>25</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2.8</v>
+      </c>
+      <c r="K101">
+        <v>1.57</v>
+      </c>
+      <c r="L101">
+        <v>1.23</v>
+      </c>
+      <c r="M101">
+        <v>6.49187352</v>
+      </c>
+      <c r="N101">
+        <v>-5.261873520000001</v>
+      </c>
+      <c r="O101">
+        <v>-1.31546838</v>
+      </c>
+      <c r="P101">
+        <v>-3.94640514</v>
+      </c>
+      <c r="Q101">
+        <v>-2.37640514</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.940194441782385</v>
+      </c>
+      <c r="T101">
+        <v>128.0994227697421</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04736691173243929</v>
+      </c>
+      <c r="W101">
+        <v>0.2274887814782935</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1894676469297571</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
